--- a/output/yearly_population_iteration_66_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_66_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3778</v>
+        <v>4976</v>
       </c>
       <c r="C2" t="n">
-        <v>6479</v>
+        <v>7574</v>
       </c>
       <c r="D2" t="n">
-        <v>25653</v>
+        <v>35708</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2878</v>
+        <v>3960</v>
       </c>
       <c r="C3" t="n">
-        <v>5598</v>
+        <v>4827</v>
       </c>
       <c r="D3" t="n">
-        <v>17730</v>
+        <v>12099</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2412</v>
+        <v>2838</v>
       </c>
       <c r="C4" t="n">
-        <v>5837</v>
+        <v>5255</v>
       </c>
       <c r="D4" t="n">
-        <v>8044</v>
+        <v>5551</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1572</v>
+        <v>1774</v>
       </c>
       <c r="C5" t="n">
-        <v>5346</v>
+        <v>4162</v>
       </c>
       <c r="D5" t="n">
-        <v>2755</v>
+        <v>2183</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>869</v>
+        <v>927</v>
       </c>
       <c r="C6" t="n">
-        <v>3363</v>
+        <v>3079</v>
       </c>
       <c r="D6" t="n">
-        <v>1121</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>416</v>
+        <v>424</v>
       </c>
       <c r="C7" t="n">
-        <v>1603</v>
+        <v>2250</v>
       </c>
       <c r="D7" t="n">
-        <v>652</v>
+        <v>632</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C8" t="n">
-        <v>705</v>
+        <v>1205</v>
       </c>
       <c r="D8" t="n">
-        <v>435</v>
+        <v>432</v>
       </c>
     </row>
     <row r="9">
@@ -881,7 +881,7 @@
         <v>64</v>
       </c>
       <c r="C9" t="n">
-        <v>326</v>
+        <v>482</v>
       </c>
       <c r="D9" t="n">
         <v>311</v>
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C10" t="n">
-        <v>212</v>
+        <v>231</v>
       </c>
       <c r="D10" t="n">
-        <v>246</v>
+        <v>243</v>
       </c>
     </row>
     <row r="11">
@@ -912,7 +912,7 @@
         <v>167</v>
       </c>
       <c r="D11" t="n">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="12">
@@ -926,7 +926,7 @@
         <v>127</v>
       </c>
       <c r="D12" t="n">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="13">
@@ -940,7 +940,7 @@
         <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="14">
@@ -951,10 +951,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="15">
@@ -968,7 +968,7 @@
         <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -979,10 +979,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -993,7 +993,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D17" t="n">
         <v>52</v>
@@ -1010,7 +1010,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1049,7 +1049,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D21" t="n">
         <v>9</v>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4895</v>
+        <v>5567</v>
       </c>
       <c r="C2" t="n">
-        <v>5988</v>
+        <v>8530</v>
       </c>
       <c r="D2" t="n">
-        <v>22514</v>
+        <v>32268</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2716</v>
+        <v>3662</v>
       </c>
       <c r="C3" t="n">
-        <v>5278</v>
+        <v>5346</v>
       </c>
       <c r="D3" t="n">
-        <v>17616</v>
+        <v>14496</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2238</v>
+        <v>2834</v>
       </c>
       <c r="C4" t="n">
-        <v>5600</v>
+        <v>4940</v>
       </c>
       <c r="D4" t="n">
-        <v>9380</v>
+        <v>6450</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1708</v>
+        <v>1967</v>
       </c>
       <c r="C5" t="n">
-        <v>5409</v>
+        <v>4539</v>
       </c>
       <c r="D5" t="n">
-        <v>3457</v>
+        <v>2613</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1064</v>
+        <v>1170</v>
       </c>
       <c r="C6" t="n">
-        <v>4224</v>
+        <v>3537</v>
       </c>
       <c r="D6" t="n">
-        <v>1356</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>551</v>
+        <v>576</v>
       </c>
       <c r="C7" t="n">
-        <v>2362</v>
+        <v>2592</v>
       </c>
       <c r="D7" t="n">
-        <v>707</v>
+        <v>674</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="C8" t="n">
-        <v>1091</v>
+        <v>1655</v>
       </c>
       <c r="D8" t="n">
-        <v>462</v>
+        <v>456</v>
       </c>
     </row>
     <row r="9">
@@ -1192,7 +1192,7 @@
         <v>91</v>
       </c>
       <c r="C9" t="n">
-        <v>478</v>
+        <v>774</v>
       </c>
       <c r="D9" t="n">
         <v>321</v>
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C10" t="n">
-        <v>257</v>
+        <v>331</v>
       </c>
       <c r="D10" t="n">
-        <v>252</v>
+        <v>249</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C11" t="n">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="D11" t="n">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="12">
@@ -1237,7 +1237,7 @@
         <v>141</v>
       </c>
       <c r="D12" t="n">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="13">
@@ -1262,10 +1262,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -1293,7 +1293,7 @@
         <v>50</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -1304,7 +1304,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D17" t="n">
         <v>52</v>
@@ -1321,7 +1321,7 @@
         <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1360,7 +1360,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D21" t="n">
         <v>10</v>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6784</v>
+        <v>6559</v>
       </c>
       <c r="C2" t="n">
-        <v>16988</v>
+        <v>13516</v>
       </c>
       <c r="D2" t="n">
-        <v>29338</v>
+        <v>32604</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2922</v>
+        <v>3626</v>
       </c>
       <c r="C3" t="n">
-        <v>4939</v>
+        <v>5910</v>
       </c>
       <c r="D3" t="n">
-        <v>17256</v>
+        <v>15959</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2080</v>
+        <v>2706</v>
       </c>
       <c r="C4" t="n">
-        <v>5341</v>
+        <v>5016</v>
       </c>
       <c r="D4" t="n">
-        <v>10190</v>
+        <v>7350</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1731</v>
+        <v>2056</v>
       </c>
       <c r="C5" t="n">
-        <v>5325</v>
+        <v>4570</v>
       </c>
       <c r="D5" t="n">
-        <v>4171</v>
+        <v>3061</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1201</v>
+        <v>1367</v>
       </c>
       <c r="C6" t="n">
-        <v>4675</v>
+        <v>3918</v>
       </c>
       <c r="D6" t="n">
-        <v>1640</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>675</v>
+        <v>724</v>
       </c>
       <c r="C7" t="n">
-        <v>3086</v>
+        <v>2945</v>
       </c>
       <c r="D7" t="n">
-        <v>781</v>
+        <v>728</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>315</v>
+        <v>325</v>
       </c>
       <c r="C8" t="n">
-        <v>1578</v>
+        <v>2005</v>
       </c>
       <c r="D8" t="n">
-        <v>490</v>
+        <v>481</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C9" t="n">
-        <v>712</v>
+        <v>1110</v>
       </c>
       <c r="D9" t="n">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="10">
@@ -1517,10 +1517,10 @@
         <v>54</v>
       </c>
       <c r="C10" t="n">
-        <v>334</v>
+        <v>488</v>
       </c>
       <c r="D10" t="n">
-        <v>258</v>
+        <v>255</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C11" t="n">
+        <v>237</v>
+      </c>
+      <c r="D11" t="n">
         <v>206</v>
-      </c>
-      <c r="D11" t="n">
-        <v>205</v>
       </c>
     </row>
     <row r="12">
@@ -1545,10 +1545,10 @@
         <v>19</v>
       </c>
       <c r="C12" t="n">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D12" t="n">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="13">
@@ -1573,10 +1573,10 @@
         <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D14" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="15">
@@ -1587,10 +1587,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -1604,7 +1604,7 @@
         <v>53</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -1629,10 +1629,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -1657,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1671,7 +1671,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D21" t="n">
         <v>11</v>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6081</v>
+        <v>6058</v>
       </c>
       <c r="C2" t="n">
-        <v>11551</v>
+        <v>9190</v>
       </c>
       <c r="D2" t="n">
-        <v>24298</v>
+        <v>26696</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3614</v>
+        <v>4591</v>
       </c>
       <c r="C3" t="n">
-        <v>8984</v>
+        <v>9366</v>
       </c>
       <c r="D3" t="n">
-        <v>18867</v>
+        <v>16965</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1599</v>
+        <v>1899</v>
       </c>
       <c r="C4" t="n">
-        <v>8034</v>
+        <v>7131</v>
       </c>
       <c r="D4" t="n">
-        <v>9535</v>
+        <v>6913</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1109</v>
+        <v>1263</v>
       </c>
       <c r="C5" t="n">
-        <v>4581</v>
+        <v>3839</v>
       </c>
       <c r="D5" t="n">
-        <v>2728</v>
+        <v>2159</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>623</v>
+        <v>668</v>
       </c>
       <c r="C6" t="n">
-        <v>3024</v>
+        <v>2886</v>
       </c>
       <c r="D6" t="n">
-        <v>765</v>
+        <v>713</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>291</v>
+        <v>300</v>
       </c>
       <c r="C7" t="n">
-        <v>1546</v>
+        <v>1964</v>
       </c>
       <c r="D7" t="n">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C8" t="n">
-        <v>697</v>
+        <v>1087</v>
       </c>
       <c r="D8" t="n">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="9">
@@ -1814,10 +1814,10 @@
         <v>49</v>
       </c>
       <c r="C9" t="n">
-        <v>327</v>
+        <v>478</v>
       </c>
       <c r="D9" t="n">
-        <v>252</v>
+        <v>249</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C10" t="n">
+        <v>232</v>
+      </c>
+      <c r="D10" t="n">
         <v>201</v>
-      </c>
-      <c r="D10" t="n">
-        <v>200</v>
       </c>
     </row>
     <row r="11">
@@ -1842,10 +1842,10 @@
         <v>17</v>
       </c>
       <c r="C11" t="n">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D11" t="n">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="12">
@@ -1870,10 +1870,10 @@
         <v>6</v>
       </c>
       <c r="C13" t="n">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D13" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D14" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="15">
@@ -1901,7 +1901,7 @@
         <v>51</v>
       </c>
       <c r="D15" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="16">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D17" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="18">
@@ -1954,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D19" t="n">
         <v>15</v>
@@ -1968,7 +1968,7 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D20" t="n">
         <v>11</v>
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3584</v>
+        <v>3793</v>
       </c>
       <c r="C2" t="n">
-        <v>4868</v>
+        <v>4392</v>
       </c>
       <c r="D2" t="n">
-        <v>16672</v>
+        <v>19366</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3978</v>
+        <v>4520</v>
       </c>
       <c r="C3" t="n">
-        <v>9197</v>
+        <v>8425</v>
       </c>
       <c r="D3" t="n">
-        <v>18518</v>
+        <v>17311</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2068</v>
+        <v>2543</v>
       </c>
       <c r="C4" t="n">
-        <v>8536</v>
+        <v>8217</v>
       </c>
       <c r="D4" t="n">
-        <v>10861</v>
+        <v>8379</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1232</v>
+        <v>1419</v>
       </c>
       <c r="C5" t="n">
-        <v>6131</v>
+        <v>5302</v>
       </c>
       <c r="D5" t="n">
-        <v>3546</v>
+        <v>2728</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>738</v>
+        <v>799</v>
       </c>
       <c r="C6" t="n">
-        <v>3746</v>
+        <v>3391</v>
       </c>
       <c r="D6" t="n">
-        <v>966</v>
+        <v>864</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>276</v>
+        <v>283</v>
       </c>
       <c r="C7" t="n">
-        <v>2057</v>
+        <v>2361</v>
       </c>
       <c r="D7" t="n">
-        <v>523</v>
+        <v>511</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C8" t="n">
-        <v>945</v>
+        <v>1397</v>
       </c>
       <c r="D8" t="n">
-        <v>340</v>
+        <v>338</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C9" t="n">
-        <v>370</v>
+        <v>526</v>
       </c>
       <c r="D9" t="n">
-        <v>260</v>
+        <v>258</v>
       </c>
     </row>
     <row r="10">
@@ -2139,7 +2139,7 @@
         <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>223</v>
+        <v>246</v>
       </c>
       <c r="D10" t="n">
         <v>210</v>
@@ -2153,10 +2153,10 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
+        <v>167</v>
+      </c>
+      <c r="D11" t="n">
         <v>166</v>
-      </c>
-      <c r="D11" t="n">
-        <v>167</v>
       </c>
     </row>
     <row r="12">
@@ -2167,7 +2167,7 @@
         <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D12" t="n">
         <v>131</v>
@@ -2181,7 +2181,7 @@
         <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D13" t="n">
         <v>97</v>
@@ -2198,7 +2198,7 @@
         <v>49</v>
       </c>
       <c r="D14" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="15">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="17">
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D18" t="n">
         <v>14</v>
@@ -2265,7 +2265,7 @@
         <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D19" t="n">
         <v>10</v>
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3995</v>
+        <v>4532</v>
       </c>
       <c r="C2" t="n">
-        <v>5793</v>
+        <v>5684</v>
       </c>
       <c r="D2" t="n">
-        <v>25867</v>
+        <v>21236</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3203</v>
+        <v>3576</v>
       </c>
       <c r="C3" t="n">
-        <v>6351</v>
+        <v>5790</v>
       </c>
       <c r="D3" t="n">
-        <v>17022</v>
+        <v>16582</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2464</v>
+        <v>2900</v>
       </c>
       <c r="C4" t="n">
-        <v>8682</v>
+        <v>8147</v>
       </c>
       <c r="D4" t="n">
-        <v>11780</v>
+        <v>9581</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1415</v>
+        <v>1684</v>
       </c>
       <c r="C5" t="n">
-        <v>7193</v>
+        <v>6562</v>
       </c>
       <c r="D5" t="n">
-        <v>4561</v>
+        <v>3513</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>873</v>
+        <v>974</v>
       </c>
       <c r="C6" t="n">
-        <v>4763</v>
+        <v>4253</v>
       </c>
       <c r="D6" t="n">
-        <v>1324</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>399</v>
+        <v>421</v>
       </c>
       <c r="C7" t="n">
-        <v>2804</v>
+        <v>2827</v>
       </c>
       <c r="D7" t="n">
-        <v>578</v>
+        <v>554</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="C8" t="n">
-        <v>1400</v>
+        <v>1797</v>
       </c>
       <c r="D8" t="n">
-        <v>359</v>
+        <v>356</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C9" t="n">
-        <v>587</v>
+        <v>855</v>
       </c>
       <c r="D9" t="n">
-        <v>269</v>
+        <v>264</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C10" t="n">
-        <v>277</v>
+        <v>346</v>
       </c>
       <c r="D10" t="n">
-        <v>212</v>
+        <v>215</v>
       </c>
     </row>
     <row r="11">
@@ -2464,10 +2464,10 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="D11" t="n">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="12">
@@ -2478,7 +2478,7 @@
         <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D12" t="n">
         <v>133</v>
@@ -2492,7 +2492,7 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D13" t="n">
         <v>100</v>
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
+        <v>35</v>
+      </c>
+      <c r="D16" t="n">
         <v>36</v>
-      </c>
-      <c r="D16" t="n">
-        <v>35</v>
       </c>
     </row>
     <row r="17">
@@ -2562,7 +2562,7 @@
         <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D18" t="n">
         <v>13</v>
@@ -2576,7 +2576,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D19" t="n">
         <v>7</v>
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2377</v>
+        <v>2683</v>
       </c>
       <c r="C2" t="n">
-        <v>2737</v>
+        <v>2660</v>
       </c>
       <c r="D2" t="n">
-        <v>18062</v>
+        <v>14821</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3269</v>
+        <v>3671</v>
       </c>
       <c r="C3" t="n">
-        <v>5970</v>
+        <v>5578</v>
       </c>
       <c r="D3" t="n">
-        <v>17560</v>
+        <v>16694</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2728</v>
+        <v>3208</v>
       </c>
       <c r="C4" t="n">
-        <v>8657</v>
+        <v>7990</v>
       </c>
       <c r="D4" t="n">
-        <v>12484</v>
+        <v>10388</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1484</v>
+        <v>1748</v>
       </c>
       <c r="C5" t="n">
-        <v>8590</v>
+        <v>7955</v>
       </c>
       <c r="D5" t="n">
-        <v>4816</v>
+        <v>3735</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>723</v>
+        <v>784</v>
       </c>
       <c r="C6" t="n">
-        <v>5639</v>
+        <v>5119</v>
       </c>
       <c r="D6" t="n">
-        <v>1296</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C7" t="n">
-        <v>2787</v>
+        <v>3099</v>
       </c>
       <c r="D7" t="n">
-        <v>579</v>
+        <v>560</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C8" t="n">
-        <v>1000</v>
+        <v>1383</v>
       </c>
       <c r="D8" t="n">
-        <v>381</v>
+        <v>376</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>271</v>
+        <v>339</v>
       </c>
       <c r="D9" t="n">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="10">
@@ -2761,10 +2761,10 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="D10" t="n">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="11">
@@ -2775,7 +2775,7 @@
         <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D11" t="n">
         <v>130</v>
@@ -2789,7 +2789,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D12" t="n">
         <v>98</v>
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
+        <v>34</v>
+      </c>
+      <c r="D15" t="n">
         <v>35</v>
-      </c>
-      <c r="D15" t="n">
-        <v>34</v>
       </c>
     </row>
     <row r="16">
@@ -2859,7 +2859,7 @@
         <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
         <v>12</v>
@@ -2873,7 +2873,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D18" t="n">
         <v>6</v>
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2928</v>
+        <v>3556</v>
       </c>
       <c r="C2" t="n">
-        <v>5272</v>
+        <v>5728</v>
       </c>
       <c r="D2" t="n">
-        <v>18788</v>
+        <v>13596</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2459</v>
+        <v>2787</v>
       </c>
       <c r="C3" t="n">
-        <v>4017</v>
+        <v>3794</v>
       </c>
       <c r="D3" t="n">
-        <v>16616</v>
+        <v>15477</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2596</v>
+        <v>2969</v>
       </c>
       <c r="C4" t="n">
-        <v>7296</v>
+        <v>6689</v>
       </c>
       <c r="D4" t="n">
-        <v>12884</v>
+        <v>11040</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1759</v>
+        <v>2082</v>
       </c>
       <c r="C5" t="n">
-        <v>8523</v>
+        <v>7881</v>
       </c>
       <c r="D5" t="n">
-        <v>5773</v>
+        <v>4579</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>919</v>
+        <v>1045</v>
       </c>
       <c r="C6" t="n">
-        <v>6861</v>
+        <v>6319</v>
       </c>
       <c r="D6" t="n">
-        <v>1752</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>270</v>
+        <v>293</v>
       </c>
       <c r="C7" t="n">
-        <v>3958</v>
+        <v>3970</v>
       </c>
       <c r="D7" t="n">
-        <v>670</v>
+        <v>630</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C8" t="n">
-        <v>1649</v>
+        <v>2031</v>
       </c>
       <c r="D8" t="n">
-        <v>402</v>
+        <v>395</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C9" t="n">
-        <v>507</v>
+        <v>686</v>
       </c>
       <c r="D9" t="n">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="10">
@@ -3072,10 +3072,10 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>210</v>
+        <v>238</v>
       </c>
       <c r="D10" t="n">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="11">
@@ -3089,7 +3089,7 @@
         <v>135</v>
       </c>
       <c r="D11" t="n">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12">
@@ -3100,7 +3100,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="D12" t="n">
         <v>99</v>
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D14" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D15" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="16">
@@ -3156,7 +3156,7 @@
         <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D16" t="n">
         <v>20</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1874</v>
+        <v>2360</v>
       </c>
       <c r="C2" t="n">
-        <v>2764</v>
+        <v>2977</v>
       </c>
       <c r="D2" t="n">
-        <v>14397</v>
+        <v>10052</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2283</v>
+        <v>2657</v>
       </c>
       <c r="C3" t="n">
-        <v>4130</v>
+        <v>4174</v>
       </c>
       <c r="D3" t="n">
-        <v>16132</v>
+        <v>14409</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2332</v>
+        <v>2660</v>
       </c>
       <c r="C4" t="n">
-        <v>5993</v>
+        <v>5511</v>
       </c>
       <c r="D4" t="n">
-        <v>13081</v>
+        <v>11406</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1916</v>
+        <v>2255</v>
       </c>
       <c r="C5" t="n">
-        <v>8237</v>
+        <v>7584</v>
       </c>
       <c r="D5" t="n">
-        <v>6403</v>
+        <v>5272</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1066</v>
+        <v>1237</v>
       </c>
       <c r="C6" t="n">
-        <v>7646</v>
+        <v>7065</v>
       </c>
       <c r="D6" t="n">
-        <v>2129</v>
+        <v>1731</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>242</v>
+        <v>264</v>
       </c>
       <c r="C7" t="n">
-        <v>4910</v>
+        <v>4816</v>
       </c>
       <c r="D7" t="n">
-        <v>747</v>
+        <v>708</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C8" t="n">
-        <v>2158</v>
+        <v>2546</v>
       </c>
       <c r="D8" t="n">
-        <v>414</v>
+        <v>407</v>
       </c>
     </row>
     <row r="9">
@@ -3366,10 +3366,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C9" t="n">
-        <v>581</v>
+        <v>789</v>
       </c>
       <c r="D9" t="n">
         <v>293</v>
@@ -3383,10 +3383,10 @@
         <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>220</v>
+        <v>240</v>
       </c>
       <c r="D10" t="n">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D11" t="n">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="12">
@@ -3411,7 +3411,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D12" t="n">
         <v>92</v>
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D13" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D14" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15">
@@ -3453,7 +3453,7 @@
         <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D15" t="n">
         <v>19</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2746</v>
+        <v>3016</v>
       </c>
       <c r="C2" t="n">
-        <v>3255</v>
+        <v>5723</v>
       </c>
       <c r="D2" t="n">
-        <v>17452</v>
+        <v>17029</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1804</v>
+        <v>2147</v>
       </c>
       <c r="C3" t="n">
-        <v>3232</v>
+        <v>3315</v>
       </c>
       <c r="D3" t="n">
-        <v>14891</v>
+        <v>12963</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2011</v>
+        <v>2310</v>
       </c>
       <c r="C4" t="n">
-        <v>5099</v>
+        <v>4831</v>
       </c>
       <c r="D4" t="n">
-        <v>13122</v>
+        <v>11491</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1894</v>
+        <v>2208</v>
       </c>
       <c r="C5" t="n">
-        <v>7182</v>
+        <v>6590</v>
       </c>
       <c r="D5" t="n">
-        <v>7105</v>
+        <v>5936</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1240</v>
+        <v>1468</v>
       </c>
       <c r="C6" t="n">
-        <v>7804</v>
+        <v>7204</v>
       </c>
       <c r="D6" t="n">
-        <v>2635</v>
+        <v>2150</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>445</v>
+        <v>502</v>
       </c>
       <c r="C7" t="n">
-        <v>5900</v>
+        <v>5651</v>
       </c>
       <c r="D7" t="n">
-        <v>901</v>
+        <v>814</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="C8" t="n">
-        <v>3122</v>
+        <v>3370</v>
       </c>
       <c r="D8" t="n">
-        <v>445</v>
+        <v>442</v>
       </c>
     </row>
     <row r="9">
@@ -3677,10 +3677,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C9" t="n">
-        <v>1075</v>
+        <v>1364</v>
       </c>
       <c r="D9" t="n">
         <v>301</v>
@@ -3694,10 +3694,10 @@
         <v>5</v>
       </c>
       <c r="C10" t="n">
-        <v>328</v>
+        <v>403</v>
       </c>
       <c r="D10" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="D11" t="n">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="12">
@@ -3725,7 +3725,7 @@
         <v>91</v>
       </c>
       <c r="D12" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D13" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D14" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="15">
@@ -3764,7 +3764,7 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D15" t="n">
         <v>18</v>
@@ -3778,7 +3778,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D16" t="n">
         <v>8</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4394</v>
+        <v>4502</v>
       </c>
       <c r="C2" t="n">
-        <v>5135</v>
+        <v>11783</v>
       </c>
       <c r="D2" t="n">
-        <v>7952</v>
+        <v>6799</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1985</v>
+        <v>2158</v>
       </c>
       <c r="C2" t="n">
-        <v>1875</v>
+        <v>3296</v>
       </c>
       <c r="D2" t="n">
-        <v>12984</v>
+        <v>12533</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2407</v>
+        <v>2842</v>
       </c>
       <c r="C3" t="n">
-        <v>3521</v>
+        <v>4114</v>
       </c>
       <c r="D3" t="n">
-        <v>16154</v>
+        <v>14306</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2777</v>
+        <v>3199</v>
       </c>
       <c r="C4" t="n">
-        <v>7480</v>
+        <v>7012</v>
       </c>
       <c r="D4" t="n">
-        <v>13420</v>
+        <v>11683</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1180</v>
+        <v>1417</v>
       </c>
       <c r="C5" t="n">
-        <v>10814</v>
+        <v>9949</v>
       </c>
       <c r="D5" t="n">
-        <v>6406</v>
+        <v>5327</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>411</v>
+        <v>463</v>
       </c>
       <c r="C6" t="n">
-        <v>7235</v>
+        <v>6949</v>
       </c>
       <c r="D6" t="n">
-        <v>2059</v>
+        <v>1747</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="C7" t="n">
-        <v>3059</v>
+        <v>3302</v>
       </c>
       <c r="D7" t="n">
-        <v>550</v>
+        <v>536</v>
       </c>
     </row>
     <row r="8">
@@ -4285,10 +4285,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C8" t="n">
-        <v>1053</v>
+        <v>1336</v>
       </c>
       <c r="D8" t="n">
         <v>294</v>
@@ -4302,10 +4302,10 @@
         <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>321</v>
+        <v>394</v>
       </c>
       <c r="D9" t="n">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="D10" t="n">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="11">
@@ -4333,7 +4333,7 @@
         <v>89</v>
       </c>
       <c r="D11" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D12" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D13" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="14">
@@ -4372,7 +4372,7 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D14" t="n">
         <v>17</v>
@@ -4386,7 +4386,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
         <v>7</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6234</v>
+        <v>6354</v>
       </c>
       <c r="C2" t="n">
-        <v>4417</v>
+        <v>7702</v>
       </c>
       <c r="D2" t="n">
-        <v>14575</v>
+        <v>8352</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1868</v>
+        <v>1914</v>
       </c>
       <c r="C3" t="n">
-        <v>2629</v>
+        <v>5938</v>
       </c>
       <c r="D3" t="n">
-        <v>1975</v>
+        <v>1781</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>79</v>
       </c>
       <c r="C4" t="n">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D4" t="n">
         <v>1538</v>
@@ -4557,7 +4557,7 @@
         <v>191</v>
       </c>
       <c r="C5" t="n">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="D5" t="n">
         <v>1161</v>
@@ -4655,7 +4655,7 @@
         <v>26</v>
       </c>
       <c r="C12" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D12" t="n">
         <v>199</v>
@@ -4669,7 +4669,7 @@
         <v>19</v>
       </c>
       <c r="C13" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D13" t="n">
         <v>170</v>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4293</v>
+        <v>4396</v>
       </c>
       <c r="C2" t="n">
-        <v>5736</v>
+        <v>4693</v>
       </c>
       <c r="D2" t="n">
-        <v>20758</v>
+        <v>14665</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3323</v>
+        <v>3391</v>
       </c>
       <c r="C3" t="n">
-        <v>3149</v>
+        <v>5981</v>
       </c>
       <c r="D3" t="n">
-        <v>3946</v>
+        <v>2753</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>845</v>
+        <v>865</v>
       </c>
       <c r="C4" t="n">
-        <v>1608</v>
+        <v>3522</v>
       </c>
       <c r="D4" t="n">
-        <v>1579</v>
+        <v>1540</v>
       </c>
     </row>
     <row r="5">
@@ -4865,10 +4865,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C5" t="n">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D5" t="n">
         <v>1186</v>
@@ -4879,10 +4879,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C6" t="n">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="D6" t="n">
         <v>864</v>
@@ -4893,7 +4893,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C7" t="n">
         <v>409</v>
@@ -4924,7 +4924,7 @@
         <v>84</v>
       </c>
       <c r="C9" t="n">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="D9" t="n">
         <v>363</v>
@@ -4938,7 +4938,7 @@
         <v>63</v>
       </c>
       <c r="C10" t="n">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D10" t="n">
         <v>352</v>
@@ -4949,7 +4949,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C11" t="n">
         <v>166</v>
@@ -4966,7 +4966,7 @@
         <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D12" t="n">
         <v>206</v>
@@ -4983,7 +4983,7 @@
         <v>103</v>
       </c>
       <c r="D13" t="n">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="14">
@@ -4994,10 +4994,10 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="15">
@@ -5022,7 +5022,7 @@
         <v>13</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D16" t="n">
         <v>98</v>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3810</v>
+        <v>4061</v>
       </c>
       <c r="C2" t="n">
-        <v>10205</v>
+        <v>5255</v>
       </c>
       <c r="D2" t="n">
-        <v>25563</v>
+        <v>20145</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3126</v>
+        <v>3196</v>
       </c>
       <c r="C3" t="n">
-        <v>3946</v>
+        <v>4569</v>
       </c>
       <c r="D3" t="n">
-        <v>6351</v>
+        <v>4460</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1761</v>
+        <v>1806</v>
       </c>
       <c r="C4" t="n">
-        <v>2431</v>
+        <v>4841</v>
       </c>
       <c r="D4" t="n">
-        <v>1985</v>
+        <v>1726</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C5" t="n">
-        <v>988</v>
+        <v>2022</v>
       </c>
       <c r="D5" t="n">
-        <v>1210</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="6">
@@ -5190,10 +5190,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C6" t="n">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="D6" t="n">
         <v>910</v>
@@ -5204,7 +5204,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C7" t="n">
         <v>409</v>
@@ -5232,10 +5232,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C9" t="n">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="D9" t="n">
         <v>372</v>
@@ -5246,10 +5246,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C10" t="n">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="D10" t="n">
         <v>346</v>
@@ -5263,7 +5263,7 @@
         <v>47</v>
       </c>
       <c r="C11" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D11" t="n">
         <v>280</v>
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C12" t="n">
         <v>148</v>
       </c>
       <c r="D12" t="n">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="13">
@@ -5291,7 +5291,7 @@
         <v>21</v>
       </c>
       <c r="C13" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D13" t="n">
         <v>173</v>
@@ -5308,7 +5308,7 @@
         <v>91</v>
       </c>
       <c r="D14" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15">
@@ -5319,10 +5319,10 @@
         <v>13</v>
       </c>
       <c r="C15" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D15" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="16">
@@ -5333,7 +5333,7 @@
         <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D16" t="n">
         <v>99</v>
@@ -5361,7 +5361,7 @@
         <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D18" t="n">
         <v>59</v>
@@ -5375,7 +5375,7 @@
         <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D19" t="n">
         <v>41</v>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4998</v>
+        <v>6421</v>
       </c>
       <c r="C2" t="n">
-        <v>10985</v>
+        <v>5943</v>
       </c>
       <c r="D2" t="n">
-        <v>26410</v>
+        <v>25234</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2844</v>
+        <v>2970</v>
       </c>
       <c r="C3" t="n">
-        <v>6282</v>
+        <v>4284</v>
       </c>
       <c r="D3" t="n">
-        <v>8824</v>
+        <v>6530</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2061</v>
+        <v>2126</v>
       </c>
       <c r="C4" t="n">
-        <v>3209</v>
+        <v>4594</v>
       </c>
       <c r="D4" t="n">
-        <v>2701</v>
+        <v>2172</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>900</v>
+        <v>903</v>
       </c>
       <c r="C5" t="n">
-        <v>1729</v>
+        <v>3421</v>
       </c>
       <c r="D5" t="n">
-        <v>1314</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="C6" t="n">
-        <v>645</v>
+        <v>1173</v>
       </c>
       <c r="D6" t="n">
-        <v>949</v>
+        <v>948</v>
       </c>
     </row>
     <row r="7">
@@ -5515,7 +5515,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C7" t="n">
         <v>354</v>
@@ -5529,10 +5529,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C8" t="n">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="D8" t="n">
         <v>484</v>
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C9" t="n">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="D9" t="n">
-        <v>378</v>
+        <v>382</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C10" t="n">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>342</v>
       </c>
     </row>
     <row r="11">
@@ -5574,10 +5574,10 @@
         <v>50</v>
       </c>
       <c r="C11" t="n">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="D11" t="n">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C12" t="n">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D12" t="n">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="13">
@@ -5602,7 +5602,7 @@
         <v>22</v>
       </c>
       <c r="C13" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D13" t="n">
         <v>176</v>
@@ -5616,10 +5616,10 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D14" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15">
@@ -5630,10 +5630,10 @@
         <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D15" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="16">
@@ -5644,10 +5644,10 @@
         <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17">
@@ -5658,10 +5658,10 @@
         <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="18">
@@ -5672,7 +5672,7 @@
         <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D18" t="n">
         <v>60</v>
@@ -5686,7 +5686,7 @@
         <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D19" t="n">
         <v>41</v>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5786</v>
+        <v>6737</v>
       </c>
       <c r="C2" t="n">
-        <v>8542</v>
+        <v>8721</v>
       </c>
       <c r="D2" t="n">
-        <v>41403</v>
+        <v>22584</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2842</v>
+        <v>3362</v>
       </c>
       <c r="C3" t="n">
-        <v>7148</v>
+        <v>4204</v>
       </c>
       <c r="D3" t="n">
-        <v>10231</v>
+        <v>8384</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1533</v>
+        <v>1572</v>
       </c>
       <c r="C4" t="n">
-        <v>4046</v>
+        <v>3622</v>
       </c>
       <c r="D4" t="n">
-        <v>3238</v>
+        <v>2531</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>770</v>
+        <v>791</v>
       </c>
       <c r="C5" t="n">
-        <v>1836</v>
+        <v>2914</v>
       </c>
       <c r="D5" t="n">
-        <v>1238</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="C6" t="n">
-        <v>798</v>
+        <v>1553</v>
       </c>
       <c r="D6" t="n">
-        <v>762</v>
+        <v>760</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C7" t="n">
-        <v>319</v>
+        <v>481</v>
       </c>
       <c r="D7" t="n">
-        <v>520</v>
+        <v>513</v>
       </c>
     </row>
     <row r="8">
@@ -5843,7 +5843,7 @@
         <v>58</v>
       </c>
       <c r="C8" t="n">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D8" t="n">
         <v>364</v>
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C9" t="n">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D9" t="n">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="10">
@@ -5874,7 +5874,7 @@
         <v>150</v>
       </c>
       <c r="D10" t="n">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="11">
@@ -5899,10 +5899,10 @@
         <v>14</v>
       </c>
       <c r="C12" t="n">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D12" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="13">
@@ -5913,10 +5913,10 @@
         <v>9</v>
       </c>
       <c r="C13" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D13" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="14">
@@ -5930,7 +5930,7 @@
         <v>57</v>
       </c>
       <c r="D14" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="15">
@@ -5941,10 +5941,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -5969,10 +5969,10 @@
         <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18">
@@ -5980,7 +5980,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C18" t="n">
         <v>33</v>
@@ -6011,7 +6011,7 @@
         <v>2</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>15</v>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4556</v>
+        <v>5604</v>
       </c>
       <c r="C2" t="n">
-        <v>6540</v>
+        <v>7453</v>
       </c>
       <c r="D2" t="n">
-        <v>36469</v>
+        <v>16680</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3591</v>
+        <v>4202</v>
       </c>
       <c r="C3" t="n">
-        <v>6843</v>
+        <v>5888</v>
       </c>
       <c r="D3" t="n">
-        <v>15046</v>
+        <v>10152</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1923</v>
+        <v>2174</v>
       </c>
       <c r="C4" t="n">
-        <v>5867</v>
+        <v>3898</v>
       </c>
       <c r="D4" t="n">
-        <v>4518</v>
+        <v>3609</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1021</v>
+        <v>1048</v>
       </c>
       <c r="C5" t="n">
-        <v>3113</v>
+        <v>3240</v>
       </c>
       <c r="D5" t="n">
-        <v>1603</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>486</v>
+        <v>494</v>
       </c>
       <c r="C6" t="n">
-        <v>1385</v>
+        <v>2317</v>
       </c>
       <c r="D6" t="n">
-        <v>835</v>
+        <v>806</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C7" t="n">
-        <v>591</v>
+        <v>1090</v>
       </c>
       <c r="D7" t="n">
-        <v>562</v>
+        <v>556</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C8" t="n">
-        <v>275</v>
+        <v>363</v>
       </c>
       <c r="D8" t="n">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="9">
@@ -6168,10 +6168,10 @@
         <v>47</v>
       </c>
       <c r="C9" t="n">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D9" t="n">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="10">
@@ -6182,10 +6182,10 @@
         <v>34</v>
       </c>
       <c r="C10" t="n">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D10" t="n">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="11">
@@ -6224,10 +6224,10 @@
         <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D13" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="14">
@@ -6252,10 +6252,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -6280,10 +6280,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -6305,7 +6305,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C19" t="n">
         <v>31</v>
@@ -6322,7 +6322,7 @@
         <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3640</v>
+        <v>5765</v>
       </c>
       <c r="C2" t="n">
-        <v>7052</v>
+        <v>5210</v>
       </c>
       <c r="D2" t="n">
-        <v>28060</v>
+        <v>26817</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3346</v>
+        <v>4022</v>
       </c>
       <c r="C3" t="n">
-        <v>5780</v>
+        <v>5835</v>
       </c>
       <c r="D3" t="n">
-        <v>17390</v>
+        <v>10465</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2367</v>
+        <v>2717</v>
       </c>
       <c r="C4" t="n">
-        <v>6297</v>
+        <v>4944</v>
       </c>
       <c r="D4" t="n">
-        <v>6402</v>
+        <v>4755</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1279</v>
+        <v>1411</v>
       </c>
       <c r="C5" t="n">
-        <v>4555</v>
+        <v>3501</v>
       </c>
       <c r="D5" t="n">
-        <v>2070</v>
+        <v>1709</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>685</v>
+        <v>696</v>
       </c>
       <c r="C6" t="n">
-        <v>2268</v>
+        <v>2786</v>
       </c>
       <c r="D6" t="n">
-        <v>963</v>
+        <v>894</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>283</v>
+        <v>290</v>
       </c>
       <c r="C7" t="n">
-        <v>1010</v>
+        <v>1738</v>
       </c>
       <c r="D7" t="n">
-        <v>598</v>
+        <v>588</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C8" t="n">
-        <v>435</v>
+        <v>733</v>
       </c>
       <c r="D8" t="n">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="9">
@@ -6476,10 +6476,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C9" t="n">
-        <v>242</v>
+        <v>282</v>
       </c>
       <c r="D9" t="n">
         <v>296</v>
@@ -6493,10 +6493,10 @@
         <v>36</v>
       </c>
       <c r="C10" t="n">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="D10" t="n">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="11">
@@ -6507,7 +6507,7 @@
         <v>25</v>
       </c>
       <c r="C11" t="n">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D11" t="n">
         <v>202</v>
@@ -6524,7 +6524,7 @@
         <v>114</v>
       </c>
       <c r="D12" t="n">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="13">
@@ -6535,10 +6535,10 @@
         <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="14">
@@ -6549,10 +6549,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15">
@@ -6563,10 +6563,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -6591,7 +6591,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D17" t="n">
         <v>52</v>
@@ -6630,10 +6630,10 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -6647,7 +6647,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D21" t="n">
         <v>8</v>

--- a/output/yearly_population_iteration_66_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_66_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4976</v>
+        <v>5611</v>
       </c>
       <c r="C2" t="n">
-        <v>7574</v>
+        <v>4599</v>
       </c>
       <c r="D2" t="n">
-        <v>35708</v>
+        <v>31140</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3960</v>
+        <v>3124</v>
       </c>
       <c r="C3" t="n">
-        <v>4827</v>
+        <v>3434</v>
       </c>
       <c r="D3" t="n">
-        <v>12099</v>
+        <v>19339</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2838</v>
+        <v>2481</v>
       </c>
       <c r="C4" t="n">
-        <v>5255</v>
+        <v>4900</v>
       </c>
       <c r="D4" t="n">
-        <v>5551</v>
+        <v>9265</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1774</v>
+        <v>1566</v>
       </c>
       <c r="C5" t="n">
-        <v>4162</v>
+        <v>4182</v>
       </c>
       <c r="D5" t="n">
-        <v>2183</v>
+        <v>3257</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>927</v>
+        <v>902</v>
       </c>
       <c r="C6" t="n">
-        <v>3079</v>
+        <v>2775</v>
       </c>
       <c r="D6" t="n">
-        <v>1006</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="C7" t="n">
-        <v>2250</v>
+        <v>1434</v>
       </c>
       <c r="D7" t="n">
-        <v>632</v>
+        <v>665</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C8" t="n">
-        <v>1205</v>
+        <v>580</v>
       </c>
       <c r="D8" t="n">
-        <v>432</v>
+        <v>436</v>
       </c>
     </row>
     <row r="9">
@@ -878,10 +878,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C9" t="n">
-        <v>482</v>
+        <v>283</v>
       </c>
       <c r="D9" t="n">
         <v>311</v>
@@ -895,10 +895,10 @@
         <v>39</v>
       </c>
       <c r="C10" t="n">
-        <v>231</v>
+        <v>206</v>
       </c>
       <c r="D10" t="n">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="11">
@@ -906,10 +906,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C11" t="n">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="D11" t="n">
         <v>205</v>
@@ -923,10 +923,10 @@
         <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D12" t="n">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="13">
@@ -940,7 +940,7 @@
         <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="14">
@@ -951,10 +951,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16">
@@ -982,7 +982,7 @@
         <v>46</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17">
@@ -993,7 +993,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D17" t="n">
         <v>52</v>
@@ -1007,7 +1007,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
         <v>39</v>
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1049,7 +1049,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D21" t="n">
         <v>9</v>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5567</v>
+        <v>6460</v>
       </c>
       <c r="C2" t="n">
-        <v>8530</v>
+        <v>5508</v>
       </c>
       <c r="D2" t="n">
-        <v>32268</v>
+        <v>30260</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3662</v>
+        <v>3429</v>
       </c>
       <c r="C3" t="n">
-        <v>5346</v>
+        <v>3491</v>
       </c>
       <c r="D3" t="n">
-        <v>14496</v>
+        <v>19644</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2834</v>
+        <v>2365</v>
       </c>
       <c r="C4" t="n">
-        <v>4940</v>
+        <v>4080</v>
       </c>
       <c r="D4" t="n">
-        <v>6450</v>
+        <v>10538</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1967</v>
+        <v>1734</v>
       </c>
       <c r="C5" t="n">
-        <v>4539</v>
+        <v>4392</v>
       </c>
       <c r="D5" t="n">
-        <v>2613</v>
+        <v>4138</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1170</v>
+        <v>1095</v>
       </c>
       <c r="C6" t="n">
-        <v>3537</v>
+        <v>3395</v>
       </c>
       <c r="D6" t="n">
-        <v>1173</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>576</v>
+        <v>565</v>
       </c>
       <c r="C7" t="n">
-        <v>2592</v>
+        <v>2023</v>
       </c>
       <c r="D7" t="n">
-        <v>674</v>
+        <v>751</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="C8" t="n">
-        <v>1655</v>
+        <v>956</v>
       </c>
       <c r="D8" t="n">
-        <v>456</v>
+        <v>460</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="C9" t="n">
-        <v>774</v>
+        <v>405</v>
       </c>
       <c r="D9" t="n">
-        <v>321</v>
+        <v>326</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C10" t="n">
-        <v>331</v>
+        <v>237</v>
       </c>
       <c r="D10" t="n">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="11">
@@ -1220,10 +1220,10 @@
         <v>28</v>
       </c>
       <c r="C11" t="n">
-        <v>189</v>
+        <v>179</v>
       </c>
       <c r="D11" t="n">
-        <v>205</v>
+        <v>208</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D12" t="n">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D13" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="14">
@@ -1262,10 +1262,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D14" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17">
@@ -1304,7 +1304,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D17" t="n">
         <v>52</v>
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1360,7 +1360,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D21" t="n">
         <v>10</v>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6559</v>
+        <v>6646</v>
       </c>
       <c r="C2" t="n">
-        <v>13516</v>
+        <v>7744</v>
       </c>
       <c r="D2" t="n">
-        <v>32604</v>
+        <v>26362</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3626</v>
+        <v>3797</v>
       </c>
       <c r="C3" t="n">
-        <v>5910</v>
+        <v>3847</v>
       </c>
       <c r="D3" t="n">
-        <v>15959</v>
+        <v>19714</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2706</v>
+        <v>2388</v>
       </c>
       <c r="C4" t="n">
-        <v>5016</v>
+        <v>3729</v>
       </c>
       <c r="D4" t="n">
-        <v>7350</v>
+        <v>11616</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2056</v>
+        <v>1791</v>
       </c>
       <c r="C5" t="n">
-        <v>4570</v>
+        <v>4123</v>
       </c>
       <c r="D5" t="n">
-        <v>3061</v>
+        <v>4894</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1367</v>
+        <v>1234</v>
       </c>
       <c r="C6" t="n">
-        <v>3918</v>
+        <v>3784</v>
       </c>
       <c r="D6" t="n">
-        <v>1364</v>
+        <v>1889</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>724</v>
+        <v>698</v>
       </c>
       <c r="C7" t="n">
-        <v>2945</v>
+        <v>2567</v>
       </c>
       <c r="D7" t="n">
-        <v>728</v>
+        <v>843</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="C8" t="n">
-        <v>2005</v>
+        <v>1374</v>
       </c>
       <c r="D8" t="n">
-        <v>481</v>
+        <v>495</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="C9" t="n">
-        <v>1110</v>
+        <v>620</v>
       </c>
       <c r="D9" t="n">
-        <v>331</v>
+        <v>336</v>
       </c>
     </row>
     <row r="10">
@@ -1514,10 +1514,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C10" t="n">
-        <v>488</v>
+        <v>297</v>
       </c>
       <c r="D10" t="n">
         <v>255</v>
@@ -1531,10 +1531,10 @@
         <v>30</v>
       </c>
       <c r="C11" t="n">
-        <v>237</v>
+        <v>199</v>
       </c>
       <c r="D11" t="n">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="12">
@@ -1545,10 +1545,10 @@
         <v>19</v>
       </c>
       <c r="C12" t="n">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="D12" t="n">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="13">
@@ -1559,10 +1559,10 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D13" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="D14" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="15">
@@ -1587,10 +1587,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16">
@@ -1604,7 +1604,7 @@
         <v>53</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17">
@@ -1629,7 +1629,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D18" t="n">
         <v>39</v>
@@ -1657,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1671,7 +1671,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D21" t="n">
         <v>11</v>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6058</v>
+        <v>6101</v>
       </c>
       <c r="C2" t="n">
-        <v>9190</v>
+        <v>5203</v>
       </c>
       <c r="D2" t="n">
-        <v>26696</v>
+        <v>21635</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4591</v>
+        <v>4493</v>
       </c>
       <c r="C3" t="n">
-        <v>9366</v>
+        <v>6152</v>
       </c>
       <c r="D3" t="n">
-        <v>16965</v>
+        <v>21836</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1899</v>
+        <v>1654</v>
       </c>
       <c r="C4" t="n">
-        <v>7131</v>
+        <v>6070</v>
       </c>
       <c r="D4" t="n">
-        <v>6913</v>
+        <v>11030</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1263</v>
+        <v>1140</v>
       </c>
       <c r="C5" t="n">
-        <v>3839</v>
+        <v>3708</v>
       </c>
       <c r="D5" t="n">
-        <v>2159</v>
+        <v>3213</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>668</v>
+        <v>644</v>
       </c>
       <c r="C6" t="n">
-        <v>2886</v>
+        <v>2515</v>
       </c>
       <c r="D6" t="n">
-        <v>713</v>
+        <v>826</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="C7" t="n">
-        <v>1964</v>
+        <v>1346</v>
       </c>
       <c r="D7" t="n">
-        <v>471</v>
+        <v>485</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="C8" t="n">
-        <v>1087</v>
+        <v>607</v>
       </c>
       <c r="D8" t="n">
-        <v>324</v>
+        <v>329</v>
       </c>
     </row>
     <row r="9">
@@ -1811,10 +1811,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C9" t="n">
-        <v>478</v>
+        <v>291</v>
       </c>
       <c r="D9" t="n">
         <v>249</v>
@@ -1828,10 +1828,10 @@
         <v>27</v>
       </c>
       <c r="C10" t="n">
-        <v>232</v>
+        <v>195</v>
       </c>
       <c r="D10" t="n">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="11">
@@ -1842,10 +1842,10 @@
         <v>17</v>
       </c>
       <c r="C11" t="n">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="D11" t="n">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="12">
@@ -1856,10 +1856,10 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D12" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C13" t="n">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="D13" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="D14" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="15">
@@ -1901,7 +1901,7 @@
         <v>51</v>
       </c>
       <c r="D15" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="16">
@@ -1926,7 +1926,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D17" t="n">
         <v>38</v>
@@ -1954,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D19" t="n">
         <v>15</v>
@@ -1968,7 +1968,7 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D20" t="n">
         <v>11</v>
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3793</v>
+        <v>3753</v>
       </c>
       <c r="C2" t="n">
-        <v>4392</v>
+        <v>2972</v>
       </c>
       <c r="D2" t="n">
-        <v>19366</v>
+        <v>15799</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4520</v>
+        <v>4489</v>
       </c>
       <c r="C3" t="n">
-        <v>8425</v>
+        <v>5176</v>
       </c>
       <c r="D3" t="n">
-        <v>17311</v>
+        <v>20550</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2543</v>
+        <v>2382</v>
       </c>
       <c r="C4" t="n">
-        <v>8217</v>
+        <v>6157</v>
       </c>
       <c r="D4" t="n">
-        <v>8379</v>
+        <v>12566</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1419</v>
+        <v>1272</v>
       </c>
       <c r="C5" t="n">
-        <v>5302</v>
+        <v>4806</v>
       </c>
       <c r="D5" t="n">
-        <v>2728</v>
+        <v>4152</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>799</v>
+        <v>773</v>
       </c>
       <c r="C6" t="n">
-        <v>3391</v>
+        <v>3091</v>
       </c>
       <c r="D6" t="n">
-        <v>864</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="C7" t="n">
-        <v>2361</v>
+        <v>1771</v>
       </c>
       <c r="D7" t="n">
-        <v>511</v>
+        <v>532</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="C8" t="n">
-        <v>1397</v>
+        <v>828</v>
       </c>
       <c r="D8" t="n">
-        <v>338</v>
+        <v>343</v>
       </c>
     </row>
     <row r="9">
@@ -2122,10 +2122,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C9" t="n">
-        <v>526</v>
+        <v>340</v>
       </c>
       <c r="D9" t="n">
         <v>258</v>
@@ -2139,10 +2139,10 @@
         <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>246</v>
+        <v>218</v>
       </c>
       <c r="D10" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="11">
@@ -2164,10 +2164,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="D12" t="n">
         <v>131</v>
@@ -2181,7 +2181,7 @@
         <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="D13" t="n">
         <v>97</v>
@@ -2198,7 +2198,7 @@
         <v>49</v>
       </c>
       <c r="D14" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="15">
@@ -2223,7 +2223,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D16" t="n">
         <v>37</v>
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D18" t="n">
         <v>14</v>
@@ -2265,7 +2265,7 @@
         <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D19" t="n">
         <v>10</v>
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4532</v>
+        <v>3748</v>
       </c>
       <c r="C2" t="n">
-        <v>5684</v>
+        <v>6004</v>
       </c>
       <c r="D2" t="n">
-        <v>21236</v>
+        <v>15835</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3576</v>
+        <v>3501</v>
       </c>
       <c r="C3" t="n">
-        <v>5790</v>
+        <v>3645</v>
       </c>
       <c r="D3" t="n">
-        <v>16582</v>
+        <v>18452</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2900</v>
+        <v>2862</v>
       </c>
       <c r="C4" t="n">
-        <v>8147</v>
+        <v>5539</v>
       </c>
       <c r="D4" t="n">
-        <v>9581</v>
+        <v>13563</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1684</v>
+        <v>1552</v>
       </c>
       <c r="C5" t="n">
-        <v>6562</v>
+        <v>5354</v>
       </c>
       <c r="D5" t="n">
-        <v>3513</v>
+        <v>5398</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>974</v>
+        <v>913</v>
       </c>
       <c r="C6" t="n">
-        <v>4253</v>
+        <v>3880</v>
       </c>
       <c r="D6" t="n">
-        <v>1121</v>
+        <v>1528</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C7" t="n">
-        <v>2827</v>
+        <v>2369</v>
       </c>
       <c r="D7" t="n">
-        <v>554</v>
+        <v>605</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="C8" t="n">
-        <v>1797</v>
+        <v>1223</v>
       </c>
       <c r="D8" t="n">
-        <v>356</v>
+        <v>368</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C9" t="n">
-        <v>855</v>
+        <v>529</v>
       </c>
       <c r="D9" t="n">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="10">
@@ -2450,7 +2450,7 @@
         <v>19</v>
       </c>
       <c r="C10" t="n">
-        <v>346</v>
+        <v>265</v>
       </c>
       <c r="D10" t="n">
         <v>215</v>
@@ -2464,7 +2464,7 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="D11" t="n">
         <v>169</v>
@@ -2475,10 +2475,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="D12" t="n">
         <v>133</v>
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="D13" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D14" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="15">
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D16" t="n">
         <v>36</v>
@@ -2551,7 +2551,7 @@
         <v>31</v>
       </c>
       <c r="D17" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="18">
@@ -2562,7 +2562,7 @@
         <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D18" t="n">
         <v>13</v>
@@ -2576,7 +2576,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D19" t="n">
         <v>7</v>
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2683</v>
+        <v>2205</v>
       </c>
       <c r="C2" t="n">
-        <v>2660</v>
+        <v>2709</v>
       </c>
       <c r="D2" t="n">
-        <v>14821</v>
+        <v>10948</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3671</v>
+        <v>3434</v>
       </c>
       <c r="C3" t="n">
-        <v>5578</v>
+        <v>4352</v>
       </c>
       <c r="D3" t="n">
-        <v>16694</v>
+        <v>17716</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3208</v>
+        <v>3158</v>
       </c>
       <c r="C4" t="n">
-        <v>7990</v>
+        <v>5354</v>
       </c>
       <c r="D4" t="n">
-        <v>10388</v>
+        <v>14271</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1748</v>
+        <v>1625</v>
       </c>
       <c r="C5" t="n">
-        <v>7955</v>
+        <v>6155</v>
       </c>
       <c r="D5" t="n">
-        <v>3735</v>
+        <v>5852</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>784</v>
+        <v>767</v>
       </c>
       <c r="C6" t="n">
-        <v>5119</v>
+        <v>4729</v>
       </c>
       <c r="D6" t="n">
-        <v>1113</v>
+        <v>1489</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="C7" t="n">
-        <v>3099</v>
+        <v>2404</v>
       </c>
       <c r="D7" t="n">
-        <v>560</v>
+        <v>605</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C8" t="n">
-        <v>1383</v>
+        <v>913</v>
       </c>
       <c r="D8" t="n">
-        <v>376</v>
+        <v>384</v>
       </c>
     </row>
     <row r="9">
@@ -2747,10 +2747,10 @@
         <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>339</v>
+        <v>259</v>
       </c>
       <c r="D9" t="n">
-        <v>288</v>
+        <v>291</v>
       </c>
     </row>
     <row r="10">
@@ -2761,7 +2761,7 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="D10" t="n">
         <v>165</v>
@@ -2772,10 +2772,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="D11" t="n">
         <v>130</v>
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="D12" t="n">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="14">
@@ -2831,7 +2831,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D15" t="n">
         <v>35</v>
@@ -2848,7 +2848,7 @@
         <v>30</v>
       </c>
       <c r="D16" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="17">
@@ -2859,7 +2859,7 @@
         <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D17" t="n">
         <v>12</v>
@@ -2873,7 +2873,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D18" t="n">
         <v>6</v>
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3556</v>
+        <v>2717</v>
       </c>
       <c r="C2" t="n">
-        <v>5728</v>
+        <v>6256</v>
       </c>
       <c r="D2" t="n">
-        <v>13596</v>
+        <v>18471</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2787</v>
+        <v>2496</v>
       </c>
       <c r="C3" t="n">
-        <v>3794</v>
+        <v>3174</v>
       </c>
       <c r="D3" t="n">
-        <v>15477</v>
+        <v>15605</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2969</v>
+        <v>2865</v>
       </c>
       <c r="C4" t="n">
-        <v>6689</v>
+        <v>4803</v>
       </c>
       <c r="D4" t="n">
-        <v>11040</v>
+        <v>14399</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2082</v>
+        <v>2001</v>
       </c>
       <c r="C5" t="n">
-        <v>7881</v>
+        <v>5716</v>
       </c>
       <c r="D5" t="n">
-        <v>4579</v>
+        <v>6967</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1045</v>
+        <v>1005</v>
       </c>
       <c r="C6" t="n">
-        <v>6319</v>
+        <v>5346</v>
       </c>
       <c r="D6" t="n">
-        <v>1450</v>
+        <v>2112</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="C7" t="n">
-        <v>3970</v>
+        <v>3407</v>
       </c>
       <c r="D7" t="n">
-        <v>630</v>
+        <v>711</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C8" t="n">
-        <v>2031</v>
+        <v>1485</v>
       </c>
       <c r="D8" t="n">
-        <v>395</v>
+        <v>409</v>
       </c>
     </row>
     <row r="9">
@@ -3058,10 +3058,10 @@
         <v>21</v>
       </c>
       <c r="C9" t="n">
-        <v>686</v>
+        <v>484</v>
       </c>
       <c r="D9" t="n">
-        <v>295</v>
+        <v>299</v>
       </c>
     </row>
     <row r="10">
@@ -3072,10 +3072,10 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>238</v>
+        <v>210</v>
       </c>
       <c r="D10" t="n">
-        <v>173</v>
+        <v>176</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="D11" t="n">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="D12" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="14">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D15" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16">
@@ -3156,7 +3156,7 @@
         <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D16" t="n">
         <v>20</v>
@@ -3170,7 +3170,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D17" t="n">
         <v>10</v>
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D18" t="n">
         <v>2</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2360</v>
+        <v>1869</v>
       </c>
       <c r="C2" t="n">
-        <v>2977</v>
+        <v>3454</v>
       </c>
       <c r="D2" t="n">
-        <v>10052</v>
+        <v>14701</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2657</v>
+        <v>2271</v>
       </c>
       <c r="C3" t="n">
-        <v>4174</v>
+        <v>4008</v>
       </c>
       <c r="D3" t="n">
-        <v>14409</v>
+        <v>15100</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2660</v>
+        <v>2514</v>
       </c>
       <c r="C4" t="n">
-        <v>5511</v>
+        <v>4153</v>
       </c>
       <c r="D4" t="n">
-        <v>11406</v>
+        <v>14261</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2255</v>
+        <v>2175</v>
       </c>
       <c r="C5" t="n">
-        <v>7584</v>
+        <v>5474</v>
       </c>
       <c r="D5" t="n">
-        <v>5272</v>
+        <v>7745</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1237</v>
+        <v>1188</v>
       </c>
       <c r="C6" t="n">
-        <v>7065</v>
+        <v>5687</v>
       </c>
       <c r="D6" t="n">
-        <v>1731</v>
+        <v>2547</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>264</v>
+        <v>290</v>
       </c>
       <c r="C7" t="n">
-        <v>4816</v>
+        <v>4133</v>
       </c>
       <c r="D7" t="n">
-        <v>708</v>
+        <v>815</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C8" t="n">
-        <v>2546</v>
+        <v>1949</v>
       </c>
       <c r="D8" t="n">
-        <v>407</v>
+        <v>433</v>
       </c>
     </row>
     <row r="9">
@@ -3369,10 +3369,10 @@
         <v>16</v>
       </c>
       <c r="C9" t="n">
-        <v>789</v>
+        <v>590</v>
       </c>
       <c r="D9" t="n">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>240</v>
+        <v>220</v>
       </c>
       <c r="D10" t="n">
-        <v>177</v>
+        <v>181</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="D11" t="n">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="D12" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="13">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D14" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="15">
@@ -3453,7 +3453,7 @@
         <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D15" t="n">
         <v>19</v>
@@ -3467,7 +3467,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D16" t="n">
         <v>9</v>
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
         <v>1</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3016</v>
+        <v>3012</v>
       </c>
       <c r="C2" t="n">
-        <v>5723</v>
+        <v>9296</v>
       </c>
       <c r="D2" t="n">
-        <v>17029</v>
+        <v>17433</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2147</v>
+        <v>1787</v>
       </c>
       <c r="C3" t="n">
-        <v>3315</v>
+        <v>3348</v>
       </c>
       <c r="D3" t="n">
-        <v>12963</v>
+        <v>14203</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2310</v>
+        <v>2108</v>
       </c>
       <c r="C4" t="n">
-        <v>4831</v>
+        <v>4002</v>
       </c>
       <c r="D4" t="n">
-        <v>11491</v>
+        <v>13811</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2208</v>
+        <v>2116</v>
       </c>
       <c r="C5" t="n">
-        <v>6590</v>
+        <v>4802</v>
       </c>
       <c r="D5" t="n">
-        <v>5936</v>
+        <v>8447</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1468</v>
+        <v>1411</v>
       </c>
       <c r="C6" t="n">
-        <v>7204</v>
+        <v>5551</v>
       </c>
       <c r="D6" t="n">
-        <v>2150</v>
+        <v>3212</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>502</v>
+        <v>527</v>
       </c>
       <c r="C7" t="n">
-        <v>5651</v>
+        <v>4781</v>
       </c>
       <c r="D7" t="n">
-        <v>814</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="C8" t="n">
-        <v>3370</v>
+        <v>2740</v>
       </c>
       <c r="D8" t="n">
-        <v>442</v>
+        <v>473</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C9" t="n">
-        <v>1364</v>
+        <v>1061</v>
       </c>
       <c r="D9" t="n">
-        <v>301</v>
+        <v>306</v>
       </c>
     </row>
     <row r="10">
@@ -3694,10 +3694,10 @@
         <v>5</v>
       </c>
       <c r="C10" t="n">
-        <v>403</v>
+        <v>338</v>
       </c>
       <c r="D10" t="n">
-        <v>185</v>
+        <v>192</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D11" t="n">
-        <v>140</v>
+        <v>137</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="D12" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D13" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
+        <v>39</v>
+      </c>
+      <c r="D14" t="n">
         <v>38</v>
-      </c>
-      <c r="D14" t="n">
-        <v>37</v>
       </c>
     </row>
     <row r="15">
@@ -3764,7 +3764,7 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D15" t="n">
         <v>18</v>
@@ -3778,7 +3778,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D16" t="n">
         <v>8</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4502</v>
+        <v>4801</v>
       </c>
       <c r="C2" t="n">
-        <v>11783</v>
+        <v>3108</v>
       </c>
       <c r="D2" t="n">
-        <v>6799</v>
+        <v>7203</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2158</v>
+        <v>2131</v>
       </c>
       <c r="C2" t="n">
-        <v>3296</v>
+        <v>5206</v>
       </c>
       <c r="D2" t="n">
-        <v>12533</v>
+        <v>12831</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2842</v>
+        <v>2458</v>
       </c>
       <c r="C3" t="n">
-        <v>4114</v>
+        <v>5059</v>
       </c>
       <c r="D3" t="n">
-        <v>14306</v>
+        <v>15546</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3199</v>
+        <v>3026</v>
       </c>
       <c r="C4" t="n">
-        <v>7012</v>
+        <v>5656</v>
       </c>
       <c r="D4" t="n">
-        <v>11683</v>
+        <v>14409</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1417</v>
+        <v>1381</v>
       </c>
       <c r="C5" t="n">
-        <v>9949</v>
+        <v>7424</v>
       </c>
       <c r="D5" t="n">
-        <v>5327</v>
+        <v>7736</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>463</v>
+        <v>486</v>
       </c>
       <c r="C6" t="n">
-        <v>6949</v>
+        <v>5882</v>
       </c>
       <c r="D6" t="n">
-        <v>1747</v>
+        <v>2439</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="C7" t="n">
-        <v>3302</v>
+        <v>2685</v>
       </c>
       <c r="D7" t="n">
-        <v>536</v>
+        <v>604</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C8" t="n">
-        <v>1336</v>
+        <v>1039</v>
       </c>
       <c r="D8" t="n">
-        <v>294</v>
+        <v>299</v>
       </c>
     </row>
     <row r="9">
@@ -4302,10 +4302,10 @@
         <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>394</v>
+        <v>331</v>
       </c>
       <c r="D9" t="n">
-        <v>181</v>
+        <v>188</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D10" t="n">
-        <v>137</v>
+        <v>134</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="D11" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D12" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
+        <v>38</v>
+      </c>
+      <c r="D13" t="n">
         <v>37</v>
-      </c>
-      <c r="D13" t="n">
-        <v>36</v>
       </c>
     </row>
     <row r="14">
@@ -4372,7 +4372,7 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D14" t="n">
         <v>17</v>
@@ -4386,7 +4386,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D15" t="n">
         <v>7</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6354</v>
+        <v>5959</v>
       </c>
       <c r="C2" t="n">
-        <v>7702</v>
+        <v>4552</v>
       </c>
       <c r="D2" t="n">
-        <v>8352</v>
+        <v>21012</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1914</v>
+        <v>2041</v>
       </c>
       <c r="C3" t="n">
-        <v>5938</v>
+        <v>1591</v>
       </c>
       <c r="D3" t="n">
-        <v>1781</v>
+        <v>1907</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>79</v>
       </c>
       <c r="C4" t="n">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D4" t="n">
         <v>1538</v>
@@ -4557,7 +4557,7 @@
         <v>191</v>
       </c>
       <c r="C5" t="n">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="D5" t="n">
         <v>1161</v>
@@ -4655,7 +4655,7 @@
         <v>26</v>
       </c>
       <c r="C12" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D12" t="n">
         <v>199</v>
@@ -4666,10 +4666,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C13" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D13" t="n">
         <v>170</v>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4396</v>
+        <v>4236</v>
       </c>
       <c r="C2" t="n">
-        <v>4693</v>
+        <v>5977</v>
       </c>
       <c r="D2" t="n">
-        <v>14665</v>
+        <v>27544</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3391</v>
+        <v>3283</v>
       </c>
       <c r="C3" t="n">
-        <v>5981</v>
+        <v>2838</v>
       </c>
       <c r="D3" t="n">
-        <v>2753</v>
+        <v>4976</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>865</v>
+        <v>920</v>
       </c>
       <c r="C4" t="n">
-        <v>3522</v>
+        <v>990</v>
       </c>
       <c r="D4" t="n">
-        <v>1540</v>
+        <v>1565</v>
       </c>
     </row>
     <row r="5">
@@ -4865,10 +4865,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C5" t="n">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D5" t="n">
         <v>1186</v>
@@ -4879,10 +4879,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C6" t="n">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="D6" t="n">
         <v>864</v>
@@ -4893,7 +4893,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C7" t="n">
         <v>409</v>
@@ -4924,7 +4924,7 @@
         <v>84</v>
       </c>
       <c r="C9" t="n">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="D9" t="n">
         <v>363</v>
@@ -4938,7 +4938,7 @@
         <v>63</v>
       </c>
       <c r="C10" t="n">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="D10" t="n">
         <v>352</v>
@@ -4949,7 +4949,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C11" t="n">
         <v>166</v>
@@ -4966,7 +4966,7 @@
         <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D12" t="n">
         <v>206</v>
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C13" t="n">
         <v>103</v>
       </c>
       <c r="D13" t="n">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C14" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15">
@@ -5022,7 +5022,7 @@
         <v>13</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D16" t="n">
         <v>98</v>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4061</v>
+        <v>4344</v>
       </c>
       <c r="C2" t="n">
-        <v>5255</v>
+        <v>8712</v>
       </c>
       <c r="D2" t="n">
-        <v>20145</v>
+        <v>32965</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3196</v>
+        <v>3087</v>
       </c>
       <c r="C3" t="n">
-        <v>4569</v>
+        <v>3938</v>
       </c>
       <c r="D3" t="n">
-        <v>4460</v>
+        <v>8228</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1806</v>
+        <v>1778</v>
       </c>
       <c r="C4" t="n">
-        <v>4841</v>
+        <v>2016</v>
       </c>
       <c r="D4" t="n">
-        <v>1726</v>
+        <v>2172</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>408</v>
+        <v>438</v>
       </c>
       <c r="C5" t="n">
-        <v>2022</v>
+        <v>634</v>
       </c>
       <c r="D5" t="n">
-        <v>1203</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="6">
@@ -5190,10 +5190,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C6" t="n">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="D6" t="n">
         <v>910</v>
@@ -5204,7 +5204,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C7" t="n">
         <v>409</v>
@@ -5232,10 +5232,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C9" t="n">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="D9" t="n">
         <v>372</v>
@@ -5246,10 +5246,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C10" t="n">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="D10" t="n">
         <v>346</v>
@@ -5263,7 +5263,7 @@
         <v>47</v>
       </c>
       <c r="C11" t="n">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D11" t="n">
         <v>280</v>
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C12" t="n">
         <v>148</v>
       </c>
       <c r="D12" t="n">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="13">
@@ -5288,10 +5288,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C13" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D13" t="n">
         <v>173</v>
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C14" t="n">
         <v>91</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="15">
@@ -5319,10 +5319,10 @@
         <v>13</v>
       </c>
       <c r="C15" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="16">
@@ -5333,7 +5333,7 @@
         <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D16" t="n">
         <v>99</v>
@@ -5347,7 +5347,7 @@
         <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D17" t="n">
         <v>79</v>
@@ -5375,7 +5375,7 @@
         <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D19" t="n">
         <v>41</v>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6421</v>
+        <v>4668</v>
       </c>
       <c r="C2" t="n">
-        <v>5943</v>
+        <v>5958</v>
       </c>
       <c r="D2" t="n">
-        <v>25234</v>
+        <v>34412</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2970</v>
+        <v>3027</v>
       </c>
       <c r="C3" t="n">
-        <v>4284</v>
+        <v>5598</v>
       </c>
       <c r="D3" t="n">
-        <v>6530</v>
+        <v>11408</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2126</v>
+        <v>2054</v>
       </c>
       <c r="C4" t="n">
-        <v>4594</v>
+        <v>3025</v>
       </c>
       <c r="D4" t="n">
-        <v>2172</v>
+        <v>3189</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>903</v>
+        <v>923</v>
       </c>
       <c r="C5" t="n">
-        <v>3421</v>
+        <v>1350</v>
       </c>
       <c r="D5" t="n">
-        <v>1245</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="6">
@@ -5501,10 +5501,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>245</v>
+        <v>254</v>
       </c>
       <c r="C6" t="n">
-        <v>1173</v>
+        <v>468</v>
       </c>
       <c r="D6" t="n">
         <v>948</v>
@@ -5515,10 +5515,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C7" t="n">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="D7" t="n">
         <v>659</v>
@@ -5529,10 +5529,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C8" t="n">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="D8" t="n">
         <v>484</v>
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C9" t="n">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="D9" t="n">
-        <v>382</v>
+        <v>378</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C10" t="n">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="D10" t="n">
-        <v>342</v>
+        <v>346</v>
       </c>
     </row>
     <row r="11">
@@ -5574,10 +5574,10 @@
         <v>50</v>
       </c>
       <c r="C11" t="n">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="D11" t="n">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C12" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D12" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="13">
@@ -5599,10 +5599,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C13" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D13" t="n">
         <v>176</v>
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C14" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="15">
@@ -5630,10 +5630,10 @@
         <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D15" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="16">
@@ -5644,10 +5644,10 @@
         <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D16" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17">
@@ -5658,10 +5658,10 @@
         <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="18">
@@ -5672,7 +5672,7 @@
         <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D18" t="n">
         <v>60</v>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6737</v>
+        <v>5798</v>
       </c>
       <c r="C2" t="n">
-        <v>8721</v>
+        <v>8166</v>
       </c>
       <c r="D2" t="n">
-        <v>22584</v>
+        <v>33241</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3362</v>
+        <v>2795</v>
       </c>
       <c r="C3" t="n">
-        <v>4204</v>
+        <v>4736</v>
       </c>
       <c r="D3" t="n">
-        <v>8384</v>
+        <v>13266</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1572</v>
+        <v>1587</v>
       </c>
       <c r="C4" t="n">
-        <v>3622</v>
+        <v>3665</v>
       </c>
       <c r="D4" t="n">
-        <v>2531</v>
+        <v>3982</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>791</v>
+        <v>776</v>
       </c>
       <c r="C5" t="n">
-        <v>2914</v>
+        <v>1636</v>
       </c>
       <c r="D5" t="n">
-        <v>1097</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>269</v>
+        <v>281</v>
       </c>
       <c r="C6" t="n">
-        <v>1553</v>
+        <v>611</v>
       </c>
       <c r="D6" t="n">
-        <v>760</v>
+        <v>766</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C7" t="n">
-        <v>481</v>
+        <v>262</v>
       </c>
       <c r="D7" t="n">
-        <v>513</v>
+        <v>520</v>
       </c>
     </row>
     <row r="8">
@@ -5843,7 +5843,7 @@
         <v>58</v>
       </c>
       <c r="C8" t="n">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D8" t="n">
         <v>364</v>
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C9" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D9" t="n">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="10">
@@ -5874,7 +5874,7 @@
         <v>150</v>
       </c>
       <c r="D10" t="n">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="11">
@@ -5899,10 +5899,10 @@
         <v>14</v>
       </c>
       <c r="C12" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D12" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C13" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D13" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="14">
@@ -5930,7 +5930,7 @@
         <v>57</v>
       </c>
       <c r="D14" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="15">
@@ -5941,10 +5941,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16">
@@ -5969,10 +5969,10 @@
         <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -5980,7 +5980,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
         <v>33</v>
@@ -6011,7 +6011,7 @@
         <v>2</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>15</v>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5604</v>
+        <v>4822</v>
       </c>
       <c r="C2" t="n">
-        <v>7453</v>
+        <v>5752</v>
       </c>
       <c r="D2" t="n">
-        <v>16680</v>
+        <v>37903</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4202</v>
+        <v>3577</v>
       </c>
       <c r="C3" t="n">
-        <v>5888</v>
+        <v>5817</v>
       </c>
       <c r="D3" t="n">
-        <v>10152</v>
+        <v>15783</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2174</v>
+        <v>1911</v>
       </c>
       <c r="C4" t="n">
-        <v>3898</v>
+        <v>4246</v>
       </c>
       <c r="D4" t="n">
-        <v>3609</v>
+        <v>5821</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1048</v>
+        <v>1061</v>
       </c>
       <c r="C5" t="n">
-        <v>3240</v>
+        <v>2809</v>
       </c>
       <c r="D5" t="n">
-        <v>1352</v>
+        <v>1824</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="C6" t="n">
-        <v>2317</v>
+        <v>1193</v>
       </c>
       <c r="D6" t="n">
-        <v>806</v>
+        <v>855</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="C7" t="n">
-        <v>1090</v>
+        <v>460</v>
       </c>
       <c r="D7" t="n">
-        <v>556</v>
+        <v>562</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C8" t="n">
-        <v>363</v>
+        <v>243</v>
       </c>
       <c r="D8" t="n">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="9">
@@ -6168,10 +6168,10 @@
         <v>47</v>
       </c>
       <c r="C9" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D9" t="n">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="10">
@@ -6182,10 +6182,10 @@
         <v>34</v>
       </c>
       <c r="C10" t="n">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D10" t="n">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="11">
@@ -6210,7 +6210,7 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D12" t="n">
         <v>152</v>
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C13" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D13" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="14">
@@ -6252,10 +6252,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16">
@@ -6280,10 +6280,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -6305,7 +6305,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C19" t="n">
         <v>31</v>
@@ -6322,7 +6322,7 @@
         <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5765</v>
+        <v>4137</v>
       </c>
       <c r="C2" t="n">
-        <v>5210</v>
+        <v>2892</v>
       </c>
       <c r="D2" t="n">
-        <v>26817</v>
+        <v>34206</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4022</v>
+        <v>3483</v>
       </c>
       <c r="C3" t="n">
-        <v>5835</v>
+        <v>5004</v>
       </c>
       <c r="D3" t="n">
-        <v>10465</v>
+        <v>18185</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2717</v>
+        <v>2339</v>
       </c>
       <c r="C4" t="n">
-        <v>4944</v>
+        <v>5006</v>
       </c>
       <c r="D4" t="n">
-        <v>4755</v>
+        <v>7556</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1411</v>
+        <v>1310</v>
       </c>
       <c r="C5" t="n">
-        <v>3501</v>
+        <v>3550</v>
       </c>
       <c r="D5" t="n">
-        <v>1709</v>
+        <v>2480</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>696</v>
+        <v>701</v>
       </c>
       <c r="C6" t="n">
-        <v>2786</v>
+        <v>2047</v>
       </c>
       <c r="D6" t="n">
-        <v>894</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="C7" t="n">
-        <v>1738</v>
+        <v>847</v>
       </c>
       <c r="D7" t="n">
-        <v>588</v>
+        <v>602</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C8" t="n">
-        <v>733</v>
+        <v>351</v>
       </c>
       <c r="D8" t="n">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
     <row r="9">
@@ -6476,10 +6476,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C9" t="n">
-        <v>282</v>
+        <v>226</v>
       </c>
       <c r="D9" t="n">
         <v>296</v>
@@ -6496,7 +6496,7 @@
         <v>191</v>
       </c>
       <c r="D10" t="n">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="11">
@@ -6521,7 +6521,7 @@
         <v>16</v>
       </c>
       <c r="C12" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D12" t="n">
         <v>155</v>
@@ -6535,10 +6535,10 @@
         <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D13" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15">
@@ -6563,10 +6563,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16">
@@ -6591,7 +6591,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D17" t="n">
         <v>52</v>
@@ -6605,7 +6605,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
         <v>38</v>
@@ -6630,10 +6630,10 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -6647,7 +6647,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D21" t="n">
         <v>8</v>

--- a/output/yearly_population_iteration_66_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_66_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5611</v>
+        <v>1445</v>
       </c>
       <c r="C2" t="n">
-        <v>4599</v>
+        <v>2708</v>
       </c>
       <c r="D2" t="n">
-        <v>31140</v>
+        <v>15719</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3124</v>
+        <v>2174</v>
       </c>
       <c r="C3" t="n">
-        <v>3434</v>
+        <v>6157</v>
       </c>
       <c r="D3" t="n">
-        <v>19339</v>
+        <v>14168</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2481</v>
+        <v>1310</v>
       </c>
       <c r="C4" t="n">
-        <v>4900</v>
+        <v>7225</v>
       </c>
       <c r="D4" t="n">
-        <v>9265</v>
+        <v>6064</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1566</v>
+        <v>723</v>
       </c>
       <c r="C5" t="n">
-        <v>4182</v>
+        <v>3927</v>
       </c>
       <c r="D5" t="n">
-        <v>3257</v>
+        <v>1993</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>902</v>
+        <v>326</v>
       </c>
       <c r="C6" t="n">
-        <v>2775</v>
+        <v>1443</v>
       </c>
       <c r="D6" t="n">
-        <v>1257</v>
+        <v>756</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>427</v>
+        <v>112</v>
       </c>
       <c r="C7" t="n">
-        <v>1434</v>
+        <v>622</v>
       </c>
       <c r="D7" t="n">
-        <v>665</v>
+        <v>491</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>165</v>
+        <v>73</v>
       </c>
       <c r="C8" t="n">
-        <v>580</v>
+        <v>347</v>
       </c>
       <c r="D8" t="n">
-        <v>436</v>
+        <v>373</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>67</v>
+        <v>54</v>
       </c>
       <c r="C9" t="n">
-        <v>283</v>
+        <v>291</v>
       </c>
       <c r="D9" t="n">
-        <v>311</v>
+        <v>319</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="C10" t="n">
-        <v>206</v>
+        <v>215</v>
       </c>
       <c r="D10" t="n">
-        <v>244</v>
+        <v>270</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="C11" t="n">
-        <v>165</v>
+        <v>177</v>
       </c>
       <c r="D11" t="n">
-        <v>205</v>
+        <v>212</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>129</v>
+        <v>111</v>
       </c>
       <c r="D12" t="n">
-        <v>158</v>
+        <v>174</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>98</v>
+        <v>78</v>
       </c>
       <c r="D13" t="n">
-        <v>125</v>
+        <v>139</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>89</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>53</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>37</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>22</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>142</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6460</v>
+        <v>1601</v>
       </c>
       <c r="C2" t="n">
-        <v>5508</v>
+        <v>4115</v>
       </c>
       <c r="D2" t="n">
-        <v>30260</v>
+        <v>15867</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3429</v>
+        <v>1536</v>
       </c>
       <c r="C3" t="n">
-        <v>3491</v>
+        <v>3760</v>
       </c>
       <c r="D3" t="n">
-        <v>19644</v>
+        <v>13532</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2365</v>
+        <v>1495</v>
       </c>
       <c r="C4" t="n">
-        <v>4080</v>
+        <v>6480</v>
       </c>
       <c r="D4" t="n">
-        <v>10538</v>
+        <v>7299</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1734</v>
+        <v>885</v>
       </c>
       <c r="C5" t="n">
-        <v>4392</v>
+        <v>5656</v>
       </c>
       <c r="D5" t="n">
-        <v>4138</v>
+        <v>2694</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1095</v>
+        <v>463</v>
       </c>
       <c r="C6" t="n">
-        <v>3395</v>
+        <v>2705</v>
       </c>
       <c r="D6" t="n">
-        <v>1535</v>
+        <v>947</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>565</v>
+        <v>180</v>
       </c>
       <c r="C7" t="n">
-        <v>2023</v>
+        <v>1030</v>
       </c>
       <c r="D7" t="n">
-        <v>751</v>
+        <v>527</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>243</v>
+        <v>82</v>
       </c>
       <c r="C8" t="n">
-        <v>956</v>
+        <v>480</v>
       </c>
       <c r="D8" t="n">
-        <v>460</v>
+        <v>386</v>
       </c>
     </row>
     <row r="9">
@@ -1189,10 +1189,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>95</v>
+        <v>57</v>
       </c>
       <c r="C9" t="n">
-        <v>405</v>
+        <v>317</v>
       </c>
       <c r="D9" t="n">
         <v>326</v>
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="C10" t="n">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="D10" t="n">
-        <v>248</v>
+        <v>275</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="C11" t="n">
-        <v>179</v>
+        <v>195</v>
       </c>
       <c r="D11" t="n">
-        <v>208</v>
+        <v>217</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="D12" t="n">
-        <v>162</v>
+        <v>176</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>109</v>
+        <v>89</v>
       </c>
       <c r="D13" t="n">
-        <v>126</v>
+        <v>142</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C14" t="n">
-        <v>84</v>
+        <v>71</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>93</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>52</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>35</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>94</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>18</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>79</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>105</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6646</v>
+        <v>836</v>
       </c>
       <c r="C2" t="n">
-        <v>7744</v>
+        <v>1664</v>
       </c>
       <c r="D2" t="n">
-        <v>26362</v>
+        <v>10705</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3797</v>
+        <v>1495</v>
       </c>
       <c r="C3" t="n">
-        <v>3847</v>
+        <v>3739</v>
       </c>
       <c r="D3" t="n">
-        <v>19714</v>
+        <v>13462</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2388</v>
+        <v>1649</v>
       </c>
       <c r="C4" t="n">
-        <v>3729</v>
+        <v>5932</v>
       </c>
       <c r="D4" t="n">
-        <v>11616</v>
+        <v>8145</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1791</v>
+        <v>917</v>
       </c>
       <c r="C5" t="n">
-        <v>4123</v>
+        <v>6527</v>
       </c>
       <c r="D5" t="n">
-        <v>4894</v>
+        <v>3090</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1234</v>
+        <v>378</v>
       </c>
       <c r="C6" t="n">
-        <v>3784</v>
+        <v>3619</v>
       </c>
       <c r="D6" t="n">
-        <v>1889</v>
+        <v>963</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>698</v>
+        <v>77</v>
       </c>
       <c r="C7" t="n">
-        <v>2567</v>
+        <v>1043</v>
       </c>
       <c r="D7" t="n">
-        <v>843</v>
+        <v>556</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>327</v>
+        <v>52</v>
       </c>
       <c r="C8" t="n">
-        <v>1374</v>
+        <v>484</v>
       </c>
       <c r="D8" t="n">
-        <v>495</v>
+        <v>436</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>134</v>
+        <v>28</v>
       </c>
       <c r="C9" t="n">
-        <v>620</v>
+        <v>243</v>
       </c>
       <c r="D9" t="n">
-        <v>336</v>
+        <v>371</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>56</v>
+        <v>14</v>
       </c>
       <c r="C10" t="n">
-        <v>297</v>
+        <v>191</v>
       </c>
       <c r="D10" t="n">
-        <v>255</v>
+        <v>212</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>199</v>
+        <v>131</v>
       </c>
       <c r="D11" t="n">
-        <v>208</v>
+        <v>172</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="C12" t="n">
-        <v>153</v>
+        <v>87</v>
       </c>
       <c r="D12" t="n">
-        <v>165</v>
+        <v>139</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>118</v>
+        <v>69</v>
       </c>
       <c r="D13" t="n">
-        <v>127</v>
+        <v>91</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>92</v>
+        <v>62</v>
       </c>
       <c r="D14" t="n">
-        <v>102</v>
+        <v>70</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>34</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="C17" t="n">
-        <v>42</v>
+        <v>92</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>17</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>35</v>
+        <v>77</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>111</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6101</v>
+        <v>913</v>
       </c>
       <c r="C2" t="n">
-        <v>5203</v>
+        <v>5390</v>
       </c>
       <c r="D2" t="n">
-        <v>21635</v>
+        <v>10010</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4493</v>
+        <v>1014</v>
       </c>
       <c r="C3" t="n">
-        <v>6152</v>
+        <v>2338</v>
       </c>
       <c r="D3" t="n">
-        <v>21836</v>
+        <v>12095</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1654</v>
+        <v>1402</v>
       </c>
       <c r="C4" t="n">
-        <v>6070</v>
+        <v>4686</v>
       </c>
       <c r="D4" t="n">
-        <v>11030</v>
+        <v>8867</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1140</v>
+        <v>1109</v>
       </c>
       <c r="C5" t="n">
-        <v>3708</v>
+        <v>6151</v>
       </c>
       <c r="D5" t="n">
-        <v>3213</v>
+        <v>3899</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>644</v>
+        <v>551</v>
       </c>
       <c r="C6" t="n">
-        <v>2515</v>
+        <v>5012</v>
       </c>
       <c r="D6" t="n">
-        <v>826</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>302</v>
+        <v>164</v>
       </c>
       <c r="C7" t="n">
-        <v>1346</v>
+        <v>2249</v>
       </c>
       <c r="D7" t="n">
-        <v>485</v>
+        <v>615</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>123</v>
+        <v>57</v>
       </c>
       <c r="C8" t="n">
-        <v>607</v>
+        <v>733</v>
       </c>
       <c r="D8" t="n">
-        <v>329</v>
+        <v>451</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="C9" t="n">
-        <v>291</v>
+        <v>339</v>
       </c>
       <c r="D9" t="n">
-        <v>249</v>
+        <v>377</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="C10" t="n">
-        <v>195</v>
+        <v>215</v>
       </c>
       <c r="D10" t="n">
-        <v>203</v>
+        <v>228</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="D11" t="n">
-        <v>161</v>
+        <v>177</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>115</v>
+        <v>101</v>
       </c>
       <c r="D12" t="n">
-        <v>124</v>
+        <v>145</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="D13" t="n">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C14" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>78</v>
+        <v>70</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>64</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="C16" t="n">
-        <v>41</v>
+        <v>89</v>
       </c>
       <c r="D16" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34</v>
+        <v>103</v>
       </c>
       <c r="D17" t="n">
-        <v>38</v>
+        <v>11</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="D18" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>111</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3753</v>
+        <v>447</v>
       </c>
       <c r="C2" t="n">
-        <v>2972</v>
+        <v>2719</v>
       </c>
       <c r="D2" t="n">
-        <v>15799</v>
+        <v>7393</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4489</v>
+        <v>851</v>
       </c>
       <c r="C3" t="n">
-        <v>5176</v>
+        <v>3364</v>
       </c>
       <c r="D3" t="n">
-        <v>20550</v>
+        <v>11114</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2382</v>
+        <v>1167</v>
       </c>
       <c r="C4" t="n">
-        <v>6157</v>
+        <v>3596</v>
       </c>
       <c r="D4" t="n">
-        <v>12566</v>
+        <v>9178</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1272</v>
+        <v>1176</v>
       </c>
       <c r="C5" t="n">
-        <v>4806</v>
+        <v>5626</v>
       </c>
       <c r="D5" t="n">
-        <v>4152</v>
+        <v>4523</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>773</v>
+        <v>677</v>
       </c>
       <c r="C6" t="n">
-        <v>3091</v>
+        <v>5692</v>
       </c>
       <c r="D6" t="n">
-        <v>1069</v>
+        <v>1562</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>285</v>
+        <v>189</v>
       </c>
       <c r="C7" t="n">
-        <v>1771</v>
+        <v>3241</v>
       </c>
       <c r="D7" t="n">
-        <v>532</v>
+        <v>689</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>105</v>
+        <v>54</v>
       </c>
       <c r="C8" t="n">
-        <v>828</v>
+        <v>1124</v>
       </c>
       <c r="D8" t="n">
-        <v>343</v>
+        <v>481</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="C9" t="n">
-        <v>340</v>
+        <v>447</v>
       </c>
       <c r="D9" t="n">
-        <v>258</v>
+        <v>379</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C10" t="n">
-        <v>218</v>
+        <v>233</v>
       </c>
       <c r="D10" t="n">
-        <v>211</v>
+        <v>236</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="D11" t="n">
-        <v>166</v>
+        <v>185</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="D12" t="n">
-        <v>131</v>
+        <v>137</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D13" t="n">
-        <v>97</v>
+        <v>94</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="D14" t="n">
-        <v>62</v>
+        <v>55</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>40</v>
+        <v>87</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>33</v>
+        <v>100</v>
       </c>
       <c r="D16" t="n">
-        <v>37</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="D17" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>108</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3748</v>
+        <v>572</v>
       </c>
       <c r="C2" t="n">
-        <v>6004</v>
+        <v>5501</v>
       </c>
       <c r="D2" t="n">
-        <v>15835</v>
+        <v>11812</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3501</v>
+        <v>574</v>
       </c>
       <c r="C3" t="n">
-        <v>3645</v>
+        <v>2681</v>
       </c>
       <c r="D3" t="n">
-        <v>18452</v>
+        <v>9920</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2862</v>
+        <v>901</v>
       </c>
       <c r="C4" t="n">
-        <v>5539</v>
+        <v>3405</v>
       </c>
       <c r="D4" t="n">
-        <v>13563</v>
+        <v>9126</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1552</v>
+        <v>1082</v>
       </c>
       <c r="C5" t="n">
-        <v>5354</v>
+        <v>4588</v>
       </c>
       <c r="D5" t="n">
-        <v>5398</v>
+        <v>5145</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>913</v>
+        <v>814</v>
       </c>
       <c r="C6" t="n">
-        <v>3880</v>
+        <v>5606</v>
       </c>
       <c r="D6" t="n">
-        <v>1528</v>
+        <v>1995</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>420</v>
+        <v>334</v>
       </c>
       <c r="C7" t="n">
-        <v>2369</v>
+        <v>4352</v>
       </c>
       <c r="D7" t="n">
-        <v>605</v>
+        <v>810</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>151</v>
+        <v>88</v>
       </c>
       <c r="C8" t="n">
-        <v>1223</v>
+        <v>2005</v>
       </c>
       <c r="D8" t="n">
-        <v>368</v>
+        <v>509</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>54</v>
+        <v>32</v>
       </c>
       <c r="C9" t="n">
-        <v>529</v>
+        <v>709</v>
       </c>
       <c r="D9" t="n">
-        <v>265</v>
+        <v>387</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C10" t="n">
-        <v>265</v>
+        <v>310</v>
       </c>
       <c r="D10" t="n">
-        <v>215</v>
+        <v>249</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C11" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D11" t="n">
-        <v>169</v>
+        <v>189</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="D12" t="n">
-        <v>133</v>
+        <v>140</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="D13" t="n">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="D14" t="n">
-        <v>65</v>
+        <v>57</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>28</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>36</v>
+        <v>104</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2205</v>
+        <v>379</v>
       </c>
       <c r="C2" t="n">
-        <v>2709</v>
+        <v>2816</v>
       </c>
       <c r="D2" t="n">
-        <v>10948</v>
+        <v>8505</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3434</v>
+        <v>804</v>
       </c>
       <c r="C3" t="n">
-        <v>4352</v>
+        <v>3669</v>
       </c>
       <c r="D3" t="n">
-        <v>17716</v>
+        <v>10723</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3158</v>
+        <v>1439</v>
       </c>
       <c r="C4" t="n">
-        <v>5354</v>
+        <v>4858</v>
       </c>
       <c r="D4" t="n">
-        <v>14271</v>
+        <v>9592</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1625</v>
+        <v>842</v>
       </c>
       <c r="C5" t="n">
-        <v>6155</v>
+        <v>7313</v>
       </c>
       <c r="D5" t="n">
-        <v>5852</v>
+        <v>4791</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>767</v>
+        <v>308</v>
       </c>
       <c r="C6" t="n">
-        <v>4729</v>
+        <v>5748</v>
       </c>
       <c r="D6" t="n">
-        <v>1489</v>
+        <v>1691</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>139</v>
+        <v>81</v>
       </c>
       <c r="C7" t="n">
-        <v>2404</v>
+        <v>1964</v>
       </c>
       <c r="D7" t="n">
-        <v>605</v>
+        <v>617</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="C8" t="n">
-        <v>913</v>
+        <v>694</v>
       </c>
       <c r="D8" t="n">
-        <v>384</v>
+        <v>379</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="C9" t="n">
-        <v>259</v>
+        <v>303</v>
       </c>
       <c r="D9" t="n">
-        <v>291</v>
+        <v>244</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D10" t="n">
-        <v>165</v>
+        <v>185</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="D11" t="n">
-        <v>130</v>
+        <v>137</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="D12" t="n">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="D13" t="n">
-        <v>63</v>
+        <v>55</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>43</v>
+        <v>86</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>27</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>35</v>
+        <v>101</v>
       </c>
       <c r="D15" t="n">
-        <v>35</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2717</v>
+        <v>231</v>
       </c>
       <c r="C2" t="n">
-        <v>6256</v>
+        <v>2041</v>
       </c>
       <c r="D2" t="n">
-        <v>18471</v>
+        <v>6187</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2496</v>
+        <v>528</v>
       </c>
       <c r="C3" t="n">
-        <v>3174</v>
+        <v>2873</v>
       </c>
       <c r="D3" t="n">
-        <v>15605</v>
+        <v>9703</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2865</v>
+        <v>955</v>
       </c>
       <c r="C4" t="n">
-        <v>4803</v>
+        <v>3982</v>
       </c>
       <c r="D4" t="n">
-        <v>14399</v>
+        <v>9109</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2001</v>
+        <v>788</v>
       </c>
       <c r="C5" t="n">
-        <v>5716</v>
+        <v>5436</v>
       </c>
       <c r="D5" t="n">
-        <v>6967</v>
+        <v>4893</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1005</v>
+        <v>307</v>
       </c>
       <c r="C6" t="n">
-        <v>5346</v>
+        <v>5358</v>
       </c>
       <c r="D6" t="n">
-        <v>2112</v>
+        <v>1816</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>298</v>
+        <v>72</v>
       </c>
       <c r="C7" t="n">
-        <v>3407</v>
+        <v>2609</v>
       </c>
       <c r="D7" t="n">
-        <v>711</v>
+        <v>610</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>66</v>
+        <v>15</v>
       </c>
       <c r="C8" t="n">
-        <v>1485</v>
+        <v>786</v>
       </c>
       <c r="D8" t="n">
-        <v>409</v>
+        <v>329</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="C9" t="n">
-        <v>484</v>
+        <v>282</v>
       </c>
       <c r="D9" t="n">
-        <v>299</v>
+        <v>195</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>210</v>
+        <v>136</v>
       </c>
       <c r="D10" t="n">
-        <v>176</v>
+        <v>142</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>137</v>
+        <v>79</v>
       </c>
       <c r="D11" t="n">
-        <v>134</v>
+        <v>101</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>85</v>
+        <v>53</v>
       </c>
       <c r="D12" t="n">
-        <v>98</v>
+        <v>63</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="D13" t="n">
-        <v>63</v>
+        <v>32</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1869</v>
+        <v>618</v>
       </c>
       <c r="C2" t="n">
-        <v>3454</v>
+        <v>5681</v>
       </c>
       <c r="D2" t="n">
-        <v>14701</v>
+        <v>7406</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2271</v>
+        <v>321</v>
       </c>
       <c r="C3" t="n">
-        <v>4008</v>
+        <v>2099</v>
       </c>
       <c r="D3" t="n">
-        <v>15100</v>
+        <v>8441</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2514</v>
+        <v>651</v>
       </c>
       <c r="C4" t="n">
-        <v>4153</v>
+        <v>3260</v>
       </c>
       <c r="D4" t="n">
-        <v>14261</v>
+        <v>8946</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2175</v>
+        <v>790</v>
       </c>
       <c r="C5" t="n">
-        <v>5474</v>
+        <v>4565</v>
       </c>
       <c r="D5" t="n">
-        <v>7745</v>
+        <v>5513</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1188</v>
+        <v>487</v>
       </c>
       <c r="C6" t="n">
-        <v>5687</v>
+        <v>5338</v>
       </c>
       <c r="D6" t="n">
-        <v>2547</v>
+        <v>2322</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>290</v>
+        <v>158</v>
       </c>
       <c r="C7" t="n">
-        <v>4133</v>
+        <v>4061</v>
       </c>
       <c r="D7" t="n">
-        <v>815</v>
+        <v>804</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>54</v>
+        <v>33</v>
       </c>
       <c r="C8" t="n">
-        <v>1949</v>
+        <v>1686</v>
       </c>
       <c r="D8" t="n">
-        <v>433</v>
+        <v>369</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C9" t="n">
-        <v>590</v>
+        <v>516</v>
       </c>
       <c r="D9" t="n">
-        <v>295</v>
+        <v>212</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C10" t="n">
-        <v>220</v>
+        <v>201</v>
       </c>
       <c r="D10" t="n">
-        <v>181</v>
+        <v>149</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>136</v>
+        <v>102</v>
       </c>
       <c r="D11" t="n">
-        <v>135</v>
+        <v>104</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="D12" t="n">
-        <v>93</v>
+        <v>67</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="D13" t="n">
-        <v>63</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="D14" t="n">
-        <v>37</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>12</v>
       </c>
       <c r="D15" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3481,10 +3481,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3012</v>
+        <v>1005</v>
       </c>
       <c r="C2" t="n">
-        <v>9296</v>
+        <v>6723</v>
       </c>
       <c r="D2" t="n">
-        <v>17433</v>
+        <v>9960</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1787</v>
+        <v>375</v>
       </c>
       <c r="C3" t="n">
-        <v>3348</v>
+        <v>3431</v>
       </c>
       <c r="D3" t="n">
-        <v>14203</v>
+        <v>7689</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2108</v>
+        <v>436</v>
       </c>
       <c r="C4" t="n">
-        <v>4002</v>
+        <v>2568</v>
       </c>
       <c r="D4" t="n">
-        <v>13811</v>
+        <v>8581</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2116</v>
+        <v>660</v>
       </c>
       <c r="C5" t="n">
-        <v>4802</v>
+        <v>3793</v>
       </c>
       <c r="D5" t="n">
-        <v>8447</v>
+        <v>5938</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1411</v>
+        <v>579</v>
       </c>
       <c r="C6" t="n">
-        <v>5551</v>
+        <v>4894</v>
       </c>
       <c r="D6" t="n">
-        <v>3212</v>
+        <v>2788</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>527</v>
+        <v>273</v>
       </c>
       <c r="C7" t="n">
-        <v>4781</v>
+        <v>4685</v>
       </c>
       <c r="D7" t="n">
-        <v>1027</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>108</v>
+        <v>76</v>
       </c>
       <c r="C8" t="n">
-        <v>2740</v>
+        <v>2802</v>
       </c>
       <c r="D8" t="n">
-        <v>473</v>
+        <v>433</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="C9" t="n">
-        <v>1061</v>
+        <v>1043</v>
       </c>
       <c r="D9" t="n">
-        <v>306</v>
+        <v>230</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D10" t="n">
-        <v>192</v>
+        <v>156</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>162</v>
+        <v>142</v>
       </c>
       <c r="D11" t="n">
-        <v>137</v>
+        <v>109</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>97</v>
+        <v>78</v>
       </c>
       <c r="D12" t="n">
-        <v>95</v>
+        <v>71</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D13" t="n">
-        <v>64</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="D14" t="n">
-        <v>38</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>57</v>
+        <v>26</v>
       </c>
       <c r="D15" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4801</v>
+        <v>5975</v>
       </c>
       <c r="C2" t="n">
-        <v>3108</v>
+        <v>8020</v>
       </c>
       <c r="D2" t="n">
-        <v>7203</v>
+        <v>12096</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>843</v>
+        <v>855</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>175</v>
+        <v>205</v>
       </c>
       <c r="C4" t="n">
-        <v>313</v>
+        <v>344</v>
       </c>
       <c r="D4" t="n">
-        <v>1805</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>249</v>
+        <v>314</v>
       </c>
       <c r="C5" t="n">
-        <v>515</v>
+        <v>586</v>
       </c>
       <c r="D5" t="n">
-        <v>1038</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>182</v>
+        <v>255</v>
       </c>
       <c r="C6" t="n">
-        <v>395</v>
+        <v>488</v>
       </c>
       <c r="D6" t="n">
-        <v>777</v>
+        <v>898</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>129</v>
+        <v>202</v>
       </c>
       <c r="C7" t="n">
-        <v>293</v>
+        <v>388</v>
       </c>
       <c r="D7" t="n">
-        <v>496</v>
+        <v>596</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>99</v>
+        <v>171</v>
       </c>
       <c r="C8" t="n">
-        <v>222</v>
+        <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>420</v>
+        <v>531</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>75</v>
+        <v>136</v>
       </c>
       <c r="C9" t="n">
-        <v>187</v>
+        <v>277</v>
       </c>
       <c r="D9" t="n">
-        <v>349</v>
+        <v>445</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>53</v>
+        <v>105</v>
       </c>
       <c r="C10" t="n">
-        <v>173</v>
+        <v>265</v>
       </c>
       <c r="D10" t="n">
-        <v>362</v>
+        <v>485</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>34</v>
+        <v>71</v>
       </c>
       <c r="C11" t="n">
-        <v>137</v>
+        <v>215</v>
       </c>
       <c r="D11" t="n">
-        <v>245</v>
+        <v>327</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="C12" t="n">
-        <v>104</v>
+        <v>169</v>
       </c>
       <c r="D12" t="n">
-        <v>196</v>
+        <v>274</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="C13" t="n">
-        <v>84</v>
+        <v>142</v>
       </c>
       <c r="D13" t="n">
-        <v>168</v>
+        <v>234</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C14" t="n">
-        <v>75</v>
+        <v>128</v>
       </c>
       <c r="D14" t="n">
-        <v>145</v>
+        <v>207</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C15" t="n">
-        <v>72</v>
+        <v>127</v>
       </c>
       <c r="D15" t="n">
-        <v>117</v>
+        <v>171</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>124</v>
       </c>
       <c r="D16" t="n">
-        <v>97</v>
+        <v>140</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="C17" t="n">
-        <v>66</v>
+        <v>119</v>
       </c>
       <c r="D17" t="n">
-        <v>76</v>
+        <v>114</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C18" t="n">
-        <v>63</v>
+        <v>116</v>
       </c>
       <c r="D18" t="n">
-        <v>57</v>
+        <v>85</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C19" t="n">
-        <v>60</v>
+        <v>111</v>
       </c>
       <c r="D19" t="n">
-        <v>38</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>109</v>
       </c>
       <c r="D20" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21">
@@ -4156,10 +4156,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C21" t="n">
-        <v>72</v>
+        <v>131</v>
       </c>
       <c r="D21" t="n">
         <v>1</v>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2131</v>
+        <v>889</v>
       </c>
       <c r="C2" t="n">
-        <v>5206</v>
+        <v>13724</v>
       </c>
       <c r="D2" t="n">
-        <v>12831</v>
+        <v>21217</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2458</v>
+        <v>522</v>
       </c>
       <c r="C3" t="n">
-        <v>5059</v>
+        <v>4356</v>
       </c>
       <c r="D3" t="n">
-        <v>15546</v>
+        <v>7481</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3026</v>
+        <v>353</v>
       </c>
       <c r="C4" t="n">
-        <v>5656</v>
+        <v>2937</v>
       </c>
       <c r="D4" t="n">
-        <v>14409</v>
+        <v>8092</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1381</v>
+        <v>524</v>
       </c>
       <c r="C5" t="n">
-        <v>7424</v>
+        <v>3137</v>
       </c>
       <c r="D5" t="n">
-        <v>7736</v>
+        <v>6188</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>486</v>
+        <v>569</v>
       </c>
       <c r="C6" t="n">
-        <v>5882</v>
+        <v>4301</v>
       </c>
       <c r="D6" t="n">
-        <v>2439</v>
+        <v>3234</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>99</v>
+        <v>364</v>
       </c>
       <c r="C7" t="n">
-        <v>2685</v>
+        <v>4777</v>
       </c>
       <c r="D7" t="n">
-        <v>604</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>21</v>
+        <v>136</v>
       </c>
       <c r="C8" t="n">
-        <v>1039</v>
+        <v>3612</v>
       </c>
       <c r="D8" t="n">
-        <v>299</v>
+        <v>518</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="C9" t="n">
-        <v>331</v>
+        <v>1756</v>
       </c>
       <c r="D9" t="n">
-        <v>188</v>
+        <v>253</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C10" t="n">
-        <v>158</v>
+        <v>619</v>
       </c>
       <c r="D10" t="n">
-        <v>134</v>
+        <v>164</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>95</v>
+        <v>216</v>
       </c>
       <c r="D11" t="n">
-        <v>93</v>
+        <v>113</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>52</v>
+        <v>101</v>
       </c>
       <c r="D12" t="n">
-        <v>62</v>
+        <v>74</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>38</v>
+        <v>63</v>
       </c>
       <c r="D13" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
         <v>55</v>
       </c>
       <c r="D14" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>68</v>
+        <v>35</v>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5959</v>
+        <v>4108</v>
       </c>
       <c r="C2" t="n">
-        <v>4552</v>
+        <v>5334</v>
       </c>
       <c r="D2" t="n">
-        <v>21012</v>
+        <v>19204</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2041</v>
+        <v>1973</v>
       </c>
       <c r="C3" t="n">
-        <v>1591</v>
+        <v>3167</v>
       </c>
       <c r="D3" t="n">
-        <v>1907</v>
+        <v>2265</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="C4" t="n">
-        <v>114</v>
+        <v>134</v>
       </c>
       <c r="D4" t="n">
-        <v>1538</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>191</v>
+        <v>148</v>
       </c>
       <c r="C5" t="n">
-        <v>384</v>
+        <v>334</v>
       </c>
       <c r="D5" t="n">
-        <v>1161</v>
+        <v>986</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>202</v>
+        <v>143</v>
       </c>
       <c r="C6" t="n">
-        <v>459</v>
+        <v>360</v>
       </c>
       <c r="D6" t="n">
-        <v>808</v>
+        <v>712</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>102</v>
       </c>
       <c r="C7" t="n">
-        <v>350</v>
+        <v>277</v>
       </c>
       <c r="D7" t="n">
-        <v>546</v>
+        <v>466</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="C8" t="n">
-        <v>260</v>
+        <v>206</v>
       </c>
       <c r="D8" t="n">
-        <v>429</v>
+        <v>384</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="C9" t="n">
-        <v>205</v>
+        <v>169</v>
       </c>
       <c r="D9" t="n">
-        <v>354</v>
+        <v>313</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="C10" t="n">
-        <v>180</v>
+        <v>153</v>
       </c>
       <c r="D10" t="n">
-        <v>356</v>
+        <v>324</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C11" t="n">
-        <v>154</v>
+        <v>128</v>
       </c>
       <c r="D11" t="n">
-        <v>261</v>
+        <v>231</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C12" t="n">
-        <v>118</v>
+        <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>199</v>
+        <v>182</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>93</v>
+        <v>79</v>
       </c>
       <c r="D13" t="n">
-        <v>170</v>
+        <v>154</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>133</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>118</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>89</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="D18" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>10</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C21" t="n">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4236</v>
+        <v>2535</v>
       </c>
       <c r="C2" t="n">
-        <v>5977</v>
+        <v>3634</v>
       </c>
       <c r="D2" t="n">
-        <v>27544</v>
+        <v>18274</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3283</v>
+        <v>2547</v>
       </c>
       <c r="C3" t="n">
-        <v>2838</v>
+        <v>3837</v>
       </c>
       <c r="D3" t="n">
-        <v>4976</v>
+        <v>5075</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>920</v>
+        <v>937</v>
       </c>
       <c r="C4" t="n">
-        <v>990</v>
+        <v>2023</v>
       </c>
       <c r="D4" t="n">
-        <v>1565</v>
+        <v>1575</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="C5" t="n">
-        <v>220</v>
+        <v>206</v>
       </c>
       <c r="D5" t="n">
-        <v>1186</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>183</v>
+        <v>135</v>
       </c>
       <c r="C6" t="n">
-        <v>411</v>
+        <v>340</v>
       </c>
       <c r="D6" t="n">
-        <v>864</v>
+        <v>756</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>161</v>
+        <v>114</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>327</v>
       </c>
       <c r="D7" t="n">
-        <v>589</v>
+        <v>509</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>115</v>
+        <v>83</v>
       </c>
       <c r="C8" t="n">
-        <v>307</v>
+        <v>244</v>
       </c>
       <c r="D8" t="n">
-        <v>441</v>
+        <v>395</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="C9" t="n">
-        <v>230</v>
+        <v>188</v>
       </c>
       <c r="D9" t="n">
-        <v>363</v>
+        <v>319</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="C10" t="n">
-        <v>192</v>
+        <v>161</v>
       </c>
       <c r="D10" t="n">
-        <v>352</v>
+        <v>318</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>140</v>
       </c>
       <c r="D11" t="n">
-        <v>270</v>
+        <v>244</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C12" t="n">
-        <v>134</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>206</v>
+        <v>187</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>170</v>
+        <v>155</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>90</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>9</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C21" t="n">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="D21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4344</v>
+        <v>2066</v>
       </c>
       <c r="C2" t="n">
-        <v>8712</v>
+        <v>8768</v>
       </c>
       <c r="D2" t="n">
-        <v>32965</v>
+        <v>25137</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3087</v>
+        <v>2096</v>
       </c>
       <c r="C3" t="n">
-        <v>3938</v>
+        <v>3194</v>
       </c>
       <c r="D3" t="n">
-        <v>8228</v>
+        <v>6918</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1778</v>
+        <v>1527</v>
       </c>
       <c r="C4" t="n">
-        <v>2016</v>
+        <v>3078</v>
       </c>
       <c r="D4" t="n">
-        <v>2172</v>
+        <v>2232</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="C5" t="n">
-        <v>634</v>
+        <v>1265</v>
       </c>
       <c r="D5" t="n">
-        <v>1207</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>146</v>
+        <v>111</v>
       </c>
       <c r="C6" t="n">
-        <v>303</v>
+        <v>259</v>
       </c>
       <c r="D6" t="n">
-        <v>910</v>
+        <v>799</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>160</v>
+        <v>116</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>334</v>
       </c>
       <c r="D7" t="n">
-        <v>625</v>
+        <v>549</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>125</v>
+        <v>91</v>
       </c>
       <c r="C8" t="n">
-        <v>358</v>
+        <v>288</v>
       </c>
       <c r="D8" t="n">
-        <v>462</v>
+        <v>407</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>91</v>
+        <v>67</v>
       </c>
       <c r="C9" t="n">
-        <v>265</v>
+        <v>218</v>
       </c>
       <c r="D9" t="n">
-        <v>372</v>
+        <v>329</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="C10" t="n">
-        <v>210</v>
+        <v>174</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>314</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="C11" t="n">
-        <v>177</v>
+        <v>149</v>
       </c>
       <c r="D11" t="n">
-        <v>280</v>
+        <v>250</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="C12" t="n">
-        <v>148</v>
+        <v>125</v>
       </c>
       <c r="D12" t="n">
-        <v>211</v>
+        <v>194</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C13" t="n">
-        <v>115</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>173</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="D14" t="n">
-        <v>149</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C15" t="n">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="D15" t="n">
-        <v>121</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C17" t="n">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C21" t="n">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4668</v>
+        <v>1747</v>
       </c>
       <c r="C2" t="n">
-        <v>5958</v>
+        <v>5397</v>
       </c>
       <c r="D2" t="n">
-        <v>34412</v>
+        <v>20499</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3027</v>
+        <v>1719</v>
       </c>
       <c r="C3" t="n">
-        <v>5598</v>
+        <v>5435</v>
       </c>
       <c r="D3" t="n">
-        <v>11408</v>
+        <v>9334</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2054</v>
+        <v>1569</v>
       </c>
       <c r="C4" t="n">
-        <v>3025</v>
+        <v>3080</v>
       </c>
       <c r="D4" t="n">
-        <v>3189</v>
+        <v>3042</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>923</v>
+        <v>847</v>
       </c>
       <c r="C5" t="n">
-        <v>1350</v>
+        <v>2248</v>
       </c>
       <c r="D5" t="n">
-        <v>1346</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>254</v>
+        <v>245</v>
       </c>
       <c r="C6" t="n">
-        <v>468</v>
+        <v>796</v>
       </c>
       <c r="D6" t="n">
-        <v>948</v>
+        <v>842</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>107</v>
       </c>
       <c r="C7" t="n">
-        <v>351</v>
+        <v>294</v>
       </c>
       <c r="D7" t="n">
-        <v>659</v>
+        <v>582</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>129</v>
+        <v>95</v>
       </c>
       <c r="C8" t="n">
-        <v>382</v>
+        <v>311</v>
       </c>
       <c r="D8" t="n">
-        <v>484</v>
+        <v>427</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>98</v>
+        <v>71</v>
       </c>
       <c r="C9" t="n">
-        <v>308</v>
+        <v>252</v>
       </c>
       <c r="D9" t="n">
-        <v>378</v>
+        <v>338</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="C10" t="n">
-        <v>232</v>
+        <v>194</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>310</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="C11" t="n">
-        <v>191</v>
+        <v>160</v>
       </c>
       <c r="D11" t="n">
-        <v>284</v>
+        <v>257</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C12" t="n">
-        <v>160</v>
+        <v>135</v>
       </c>
       <c r="D12" t="n">
-        <v>218</v>
+        <v>200</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C13" t="n">
-        <v>127</v>
+        <v>108</v>
       </c>
       <c r="D13" t="n">
-        <v>176</v>
+        <v>159</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="D14" t="n">
-        <v>149</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="D15" t="n">
-        <v>123</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C16" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C17" t="n">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>80</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C18" t="n">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C21" t="n">
-        <v>137</v>
+        <v>120</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5798</v>
+        <v>2494</v>
       </c>
       <c r="C2" t="n">
-        <v>8166</v>
+        <v>6890</v>
       </c>
       <c r="D2" t="n">
-        <v>33241</v>
+        <v>28394</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2795</v>
+        <v>1447</v>
       </c>
       <c r="C3" t="n">
-        <v>4736</v>
+        <v>4704</v>
       </c>
       <c r="D3" t="n">
-        <v>13266</v>
+        <v>10373</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1587</v>
+        <v>1410</v>
       </c>
       <c r="C4" t="n">
-        <v>3665</v>
+        <v>4304</v>
       </c>
       <c r="D4" t="n">
-        <v>3982</v>
+        <v>4067</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>776</v>
+        <v>1053</v>
       </c>
       <c r="C5" t="n">
-        <v>1636</v>
+        <v>2640</v>
       </c>
       <c r="D5" t="n">
-        <v>1330</v>
+        <v>1564</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>281</v>
+        <v>473</v>
       </c>
       <c r="C6" t="n">
-        <v>611</v>
+        <v>1526</v>
       </c>
       <c r="D6" t="n">
-        <v>766</v>
+        <v>906</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>87</v>
+        <v>155</v>
       </c>
       <c r="C7" t="n">
-        <v>262</v>
+        <v>541</v>
       </c>
       <c r="D7" t="n">
-        <v>520</v>
+        <v>613</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>58</v>
+        <v>94</v>
       </c>
       <c r="C8" t="n">
-        <v>222</v>
+        <v>302</v>
       </c>
       <c r="D8" t="n">
-        <v>364</v>
+        <v>448</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>45</v>
+        <v>74</v>
       </c>
       <c r="C9" t="n">
-        <v>200</v>
+        <v>279</v>
       </c>
       <c r="D9" t="n">
-        <v>270</v>
+        <v>345</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="C10" t="n">
-        <v>150</v>
+        <v>220</v>
       </c>
       <c r="D10" t="n">
-        <v>237</v>
+        <v>311</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="C11" t="n">
-        <v>114</v>
+        <v>174</v>
       </c>
       <c r="D11" t="n">
-        <v>193</v>
+        <v>262</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>93</v>
+        <v>145</v>
       </c>
       <c r="D12" t="n">
-        <v>149</v>
+        <v>203</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="C13" t="n">
-        <v>73</v>
+        <v>117</v>
       </c>
       <c r="D13" t="n">
-        <v>116</v>
+        <v>163</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>94</v>
       </c>
       <c r="D14" t="n">
-        <v>97</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>45</v>
+        <v>77</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C16" t="n">
-        <v>38</v>
+        <v>67</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>53</v>
       </c>
       <c r="D20" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>75</v>
+        <v>133</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4822</v>
+        <v>3360</v>
       </c>
       <c r="C2" t="n">
-        <v>5752</v>
+        <v>9332</v>
       </c>
       <c r="D2" t="n">
-        <v>37903</v>
+        <v>27457</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3577</v>
+        <v>1575</v>
       </c>
       <c r="C3" t="n">
-        <v>5817</v>
+        <v>5053</v>
       </c>
       <c r="D3" t="n">
-        <v>15783</v>
+        <v>12254</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1911</v>
+        <v>1239</v>
       </c>
       <c r="C4" t="n">
-        <v>4246</v>
+        <v>4421</v>
       </c>
       <c r="D4" t="n">
-        <v>5821</v>
+        <v>4993</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1061</v>
+        <v>1080</v>
       </c>
       <c r="C5" t="n">
-        <v>2809</v>
+        <v>3415</v>
       </c>
       <c r="D5" t="n">
-        <v>1824</v>
+        <v>1948</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>493</v>
+        <v>670</v>
       </c>
       <c r="C6" t="n">
-        <v>1193</v>
+        <v>2029</v>
       </c>
       <c r="D6" t="n">
-        <v>855</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>167</v>
+        <v>262</v>
       </c>
       <c r="C7" t="n">
-        <v>460</v>
+        <v>1013</v>
       </c>
       <c r="D7" t="n">
-        <v>562</v>
+        <v>646</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>67</v>
+        <v>110</v>
       </c>
       <c r="C8" t="n">
-        <v>243</v>
+        <v>411</v>
       </c>
       <c r="D8" t="n">
-        <v>389</v>
+        <v>469</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>47</v>
+        <v>75</v>
       </c>
       <c r="C9" t="n">
-        <v>211</v>
+        <v>289</v>
       </c>
       <c r="D9" t="n">
-        <v>281</v>
+        <v>353</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>34</v>
+        <v>58</v>
       </c>
       <c r="C10" t="n">
-        <v>173</v>
+        <v>242</v>
       </c>
       <c r="D10" t="n">
-        <v>240</v>
+        <v>312</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="C11" t="n">
-        <v>131</v>
+        <v>192</v>
       </c>
       <c r="D11" t="n">
-        <v>198</v>
+        <v>266</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="C12" t="n">
-        <v>103</v>
+        <v>156</v>
       </c>
       <c r="D12" t="n">
-        <v>152</v>
+        <v>206</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="C13" t="n">
-        <v>82</v>
+        <v>127</v>
       </c>
       <c r="D13" t="n">
-        <v>119</v>
+        <v>166</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>64</v>
+        <v>101</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>50</v>
+        <v>82</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>115</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>93</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>63</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>53</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="C21" t="n">
-        <v>83</v>
+        <v>145</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4137</v>
+        <v>2929</v>
       </c>
       <c r="C2" t="n">
-        <v>2892</v>
+        <v>5673</v>
       </c>
       <c r="D2" t="n">
-        <v>34206</v>
+        <v>21424</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3483</v>
+        <v>2155</v>
       </c>
       <c r="C3" t="n">
-        <v>5004</v>
+        <v>8085</v>
       </c>
       <c r="D3" t="n">
-        <v>18185</v>
+        <v>13695</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2339</v>
+        <v>997</v>
       </c>
       <c r="C4" t="n">
-        <v>5006</v>
+        <v>6079</v>
       </c>
       <c r="D4" t="n">
-        <v>7556</v>
+        <v>4693</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1310</v>
+        <v>619</v>
       </c>
       <c r="C5" t="n">
-        <v>3550</v>
+        <v>1988</v>
       </c>
       <c r="D5" t="n">
-        <v>2480</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>701</v>
+        <v>242</v>
       </c>
       <c r="C6" t="n">
-        <v>2047</v>
+        <v>992</v>
       </c>
       <c r="D6" t="n">
-        <v>1019</v>
+        <v>633</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>292</v>
+        <v>101</v>
       </c>
       <c r="C7" t="n">
-        <v>847</v>
+        <v>402</v>
       </c>
       <c r="D7" t="n">
-        <v>602</v>
+        <v>459</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>102</v>
+        <v>69</v>
       </c>
       <c r="C8" t="n">
-        <v>351</v>
+        <v>283</v>
       </c>
       <c r="D8" t="n">
-        <v>415</v>
+        <v>345</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C9" t="n">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="D9" t="n">
-        <v>296</v>
+        <v>305</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C10" t="n">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="D10" t="n">
-        <v>241</v>
+        <v>260</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C11" t="n">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D11" t="n">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="D12" t="n">
-        <v>155</v>
+        <v>162</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>122</v>
+        <v>133</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C14" t="n">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>112</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>91</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C16" t="n">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>74</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
     <row r="18">
@@ -6602,10 +6602,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="D18" t="n">
         <v>38</v>
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>145</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>91</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
